--- a/backend/API/SeedData.xlsx
+++ b/backend/API/SeedData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakub\Desktop\Cs\pc\RestaurantOrderingAppSolution\backend\API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{42C55267-5170-4C7E-AAD2-8038AE42D5BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8295F21A-AFD8-4313-9FB9-B37234989A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="1908" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{C8CF7BA1-E9AA-4852-A9EB-5F1AD6BFABCB}"/>
+    <workbookView xWindow="28680" yWindow="-3255" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{C8CF7BA1-E9AA-4852-A9EB-5F1AD6BFABCB}"/>
   </bookViews>
   <sheets>
     <sheet name="CustomerInformation" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1030" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="397">
   <si>
     <t>Id</t>
   </si>
@@ -462,99 +462,6 @@
     <t>SubCategoryId</t>
   </si>
   <si>
-    <t>Numer 1</t>
-  </si>
-  <si>
-    <t>Numer 2</t>
-  </si>
-  <si>
-    <t>Numer 3</t>
-  </si>
-  <si>
-    <t>Numer 4</t>
-  </si>
-  <si>
-    <t>Numer 5</t>
-  </si>
-  <si>
-    <t>Numer 6</t>
-  </si>
-  <si>
-    <t>Numer 7</t>
-  </si>
-  <si>
-    <t>Numer 8</t>
-  </si>
-  <si>
-    <t>Numer 9</t>
-  </si>
-  <si>
-    <t>Numer 10</t>
-  </si>
-  <si>
-    <t>Numer 11</t>
-  </si>
-  <si>
-    <t>Numer 12</t>
-  </si>
-  <si>
-    <t>Numer 13</t>
-  </si>
-  <si>
-    <t>Numer 14</t>
-  </si>
-  <si>
-    <t>Numer 15</t>
-  </si>
-  <si>
-    <t>Numer 16</t>
-  </si>
-  <si>
-    <t>Numer 17</t>
-  </si>
-  <si>
-    <t>Numer 18</t>
-  </si>
-  <si>
-    <t>Numer 19</t>
-  </si>
-  <si>
-    <t>Numer 20</t>
-  </si>
-  <si>
-    <t>Numer 21</t>
-  </si>
-  <si>
-    <t>Numer 22</t>
-  </si>
-  <si>
-    <t>Numer 23</t>
-  </si>
-  <si>
-    <t>Numer 24</t>
-  </si>
-  <si>
-    <t>Numer 25</t>
-  </si>
-  <si>
-    <t>Numer 26</t>
-  </si>
-  <si>
-    <t>Numer 27</t>
-  </si>
-  <si>
-    <t>Numer 28</t>
-  </si>
-  <si>
-    <t>Numer 29</t>
-  </si>
-  <si>
-    <t>Numer 30</t>
-  </si>
-  <si>
-    <t>Numer 31</t>
-  </si>
-  <si>
     <t>Numer 32</t>
   </si>
   <si>
@@ -720,27 +627,12 @@
     <t>0088ce77-b10d-4843-a60d-59f5906af4d6</t>
   </si>
   <si>
-    <t>Piwo Lane</t>
-  </si>
-  <si>
-    <t>Pepsi</t>
-  </si>
-  <si>
-    <t>Coca Cola</t>
-  </si>
-  <si>
     <t>Yotea Yoga</t>
   </si>
   <si>
     <t>Tymbark</t>
   </si>
   <si>
-    <t>Lemoniada cytrynowa</t>
-  </si>
-  <si>
-    <t>Herbata zimowa</t>
-  </si>
-  <si>
     <t>449a4970-325d-4550-995a-561306f92bf2</t>
   </si>
   <si>
@@ -1054,6 +946,297 @@
   </si>
   <si>
     <t>Ogródek</t>
+  </si>
+  <si>
+    <t>Rossa 1</t>
+  </si>
+  <si>
+    <t>Rossa 3</t>
+  </si>
+  <si>
+    <t>Rossa 6</t>
+  </si>
+  <si>
+    <t>Rossa 8</t>
+  </si>
+  <si>
+    <t>Rossa 12</t>
+  </si>
+  <si>
+    <t>Rossa 13</t>
+  </si>
+  <si>
+    <t>Rossa 14</t>
+  </si>
+  <si>
+    <t>Rossa 15</t>
+  </si>
+  <si>
+    <t>Rossa 16</t>
+  </si>
+  <si>
+    <t>Rossa 20</t>
+  </si>
+  <si>
+    <t>Rossa 21</t>
+  </si>
+  <si>
+    <t>Rossa 23</t>
+  </si>
+  <si>
+    <t>Rossa 25</t>
+  </si>
+  <si>
+    <t>Rossa 28</t>
+  </si>
+  <si>
+    <t>Rossa 30</t>
+  </si>
+  <si>
+    <t>Special 2</t>
+  </si>
+  <si>
+    <t>Special 7</t>
+  </si>
+  <si>
+    <t>Special 17</t>
+  </si>
+  <si>
+    <t>Special 18</t>
+  </si>
+  <si>
+    <t>Special 19</t>
+  </si>
+  <si>
+    <t>Special 22</t>
+  </si>
+  <si>
+    <t>Special 24</t>
+  </si>
+  <si>
+    <t>Special 27</t>
+  </si>
+  <si>
+    <t>Special 31</t>
+  </si>
+  <si>
+    <t>Bianca 4</t>
+  </si>
+  <si>
+    <t>Bianca 5</t>
+  </si>
+  <si>
+    <t>Bianca 9</t>
+  </si>
+  <si>
+    <t>Bianca 10</t>
+  </si>
+  <si>
+    <t>Bianca 11</t>
+  </si>
+  <si>
+    <t>Bianca 29</t>
+  </si>
+  <si>
+    <t>Panuozzo 1</t>
+  </si>
+  <si>
+    <t>Panuozzo 2</t>
+  </si>
+  <si>
+    <t>Piadina 1</t>
+  </si>
+  <si>
+    <t>Piadina 2</t>
+  </si>
+  <si>
+    <t>Lemoniada Truskawkowa</t>
+  </si>
+  <si>
+    <t>Lemoniada Arbuzowa</t>
+  </si>
+  <si>
+    <t>Lemoniada Cytrynowa</t>
+  </si>
+  <si>
+    <t>Herbata Zimowa</t>
+  </si>
+  <si>
+    <t>Lemoniada Grejpfrutowa</t>
+  </si>
+  <si>
+    <t>Kawa Mrożona</t>
+  </si>
+  <si>
+    <t>Kawa Mrożona z Lodami</t>
+  </si>
+  <si>
+    <t>Grzaniec Piwny</t>
+  </si>
+  <si>
+    <t>Grzaniec Winny</t>
+  </si>
+  <si>
+    <t>Gorąca Czekolada</t>
+  </si>
+  <si>
+    <t>Cappucino</t>
+  </si>
+  <si>
+    <t>Latte Macchiato</t>
+  </si>
+  <si>
+    <t>Espresso</t>
+  </si>
+  <si>
+    <t>Herbata</t>
+  </si>
+  <si>
+    <t>0.2L Pepsi</t>
+  </si>
+  <si>
+    <t>0.5L Pepsi</t>
+  </si>
+  <si>
+    <t>0.25L Coca Cola</t>
+  </si>
+  <si>
+    <t>Polara</t>
+  </si>
+  <si>
+    <t>0.2L Soki owocowe</t>
+  </si>
+  <si>
+    <t>Dzbanek Soku</t>
+  </si>
+  <si>
+    <t>Dzbanek Wody</t>
+  </si>
+  <si>
+    <t>Woda Gazowana</t>
+  </si>
+  <si>
+    <t>Woda Niegazowana</t>
+  </si>
+  <si>
+    <t>Calzone 1</t>
+  </si>
+  <si>
+    <t>Calzone 2</t>
+  </si>
+  <si>
+    <t>Calzone 3</t>
+  </si>
+  <si>
+    <t>Calzone 4</t>
+  </si>
+  <si>
+    <t>Calzone 5</t>
+  </si>
+  <si>
+    <t>Calzone 6</t>
+  </si>
+  <si>
+    <t>0.5L Coca Cola</t>
+  </si>
+  <si>
+    <t>0.3L Piwo Lane Lager</t>
+  </si>
+  <si>
+    <t>0.5L Piwo Lane Lager</t>
+  </si>
+  <si>
+    <t>0.3L Piwo Lane Pszeniczne</t>
+  </si>
+  <si>
+    <t>0.5L Piwo Lane Pszeniczne</t>
+  </si>
+  <si>
+    <t>cbcdabf2-86fc-4a18-a31f-d81a86a76ed6</t>
+  </si>
+  <si>
+    <t>2c2b498d-8989-4598-87be-77ddd465ba43</t>
+  </si>
+  <si>
+    <t>508a4a8c-206f-4de5-8ed5-d174c2a351c6</t>
+  </si>
+  <si>
+    <t>35b8c735-ef56-423c-a63e-bb084cc9d280</t>
+  </si>
+  <si>
+    <t>dc71fe21-c3f5-434a-8719-437f172fed3f</t>
+  </si>
+  <si>
+    <t>96c745c4-ce87-409d-8577-b363a7cd03e6</t>
+  </si>
+  <si>
+    <t>a689894e-77d7-4034-b454-156aca341f73</t>
+  </si>
+  <si>
+    <t>80770e76-f663-4164-b48d-c0f7ede3768c</t>
+  </si>
+  <si>
+    <t>d49191ca-4fcd-4fa3-9f67-12f6681fe5fe</t>
+  </si>
+  <si>
+    <t>cc31099a-3298-4140-a2e6-1509c61d34bf</t>
+  </si>
+  <si>
+    <t>9eb269ef-b7a3-468d-a48b-2245b89cdaf9</t>
+  </si>
+  <si>
+    <t>8fb42c46-21b5-4fe1-b3a9-11e136bf662f</t>
+  </si>
+  <si>
+    <t>ec16b560-cd2e-47a9-991f-f77c26d9f202</t>
+  </si>
+  <si>
+    <t>1bb2386e-b0fe-47ee-9df0-3a819aa8dd69</t>
+  </si>
+  <si>
+    <t>048ee6c3-7141-44e1-b44d-3657186f9c36</t>
+  </si>
+  <si>
+    <t>80577c59-8251-4b70-a0f3-fcfebb7a5a8a</t>
+  </si>
+  <si>
+    <t>d30412b5-cfdd-4f0b-92dd-33e6bda55a1f</t>
+  </si>
+  <si>
+    <t>edb49138-644c-447a-b7a2-dd27f1ab316c</t>
+  </si>
+  <si>
+    <t>d63d954b-b15f-47c3-965b-6bec1a4a544a</t>
+  </si>
+  <si>
+    <t>821a0772-57f9-4c93-a899-1bf74270b651</t>
+  </si>
+  <si>
+    <t>a7adf375-192d-49fd-bafe-099b693fea52</t>
+  </si>
+  <si>
+    <t>13d6c318-bf73-4803-bbfc-bb32ef7b06d5</t>
+  </si>
+  <si>
+    <t>a5c2205a-1f9f-48ed-9776-d456abdabbc1</t>
+  </si>
+  <si>
+    <t>b7b02011-f4bf-404d-899e-7cb3f73fd3f6</t>
+  </si>
+  <si>
+    <t>7fe3af9e-f104-41bc-8a08-978e69b7d550</t>
+  </si>
+  <si>
+    <t>449f15ff-3d3b-4c09-93b3-85a6fbfd4053</t>
+  </si>
+  <si>
+    <t>6f5b0762-ef40-4a98-ad04-31de6f33ecd0</t>
+  </si>
+  <si>
+    <t>Pistacje</t>
+  </si>
+  <si>
+    <t>5820a2b2-2eb1-4647-87c8-3a77cc77047c</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1273,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1113,11 +1296,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1147,6 +1343,21 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1464,16 +1675,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA11DBA6-6284-4357-AB5F-3F63D3FCE544}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="39.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" customWidth="1"/>
-    <col min="5" max="5" width="26.85546875" customWidth="1"/>
-    <col min="6" max="6" width="21.28515625" customWidth="1"/>
-    <col min="7" max="7" width="32.28515625" customWidth="1"/>
-    <col min="8" max="8" width="36.85546875" customWidth="1"/>
+    <col min="1" max="1" width="39.44140625" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" customWidth="1"/>
+    <col min="4" max="4" width="15.33203125" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" customWidth="1"/>
+    <col min="6" max="6" width="21.33203125" customWidth="1"/>
+    <col min="7" max="7" width="32.33203125" customWidth="1"/>
+    <col min="8" max="8" width="36.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1567,15 +1778,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4966BB-B585-4EFD-A171-2B6D26A10B97}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" customWidth="1"/>
-    <col min="8" max="8" width="37.42578125" customWidth="1"/>
-    <col min="9" max="9" width="36.42578125" customWidth="1"/>
+    <col min="1" max="1" width="36.5546875" customWidth="1"/>
+    <col min="2" max="2" width="23.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.109375" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="6" width="8.88671875" customWidth="1"/>
+    <col min="8" max="8" width="37.44140625" customWidth="1"/>
+    <col min="9" max="9" width="36.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1583,28 +1794,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>295</v>
+        <v>259</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>296</v>
+        <v>260</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>298</v>
+        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1624,16 +1835,16 @@
         <v>0</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>303</v>
+        <v>267</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -1653,13 +1864,13 @@
         <v>0</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>302</v>
+        <v>266</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>12</v>
@@ -1667,7 +1878,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="2" t="s">
-        <v>304</v>
+        <v>268</v>
       </c>
       <c r="B4" s="10">
         <v>45758.618055555555</v>
@@ -1682,16 +1893,16 @@
         <v>0</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>301</v>
+        <v>265</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -1701,411 +1912,4243 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2E4AC9-0CD2-4F25-AD3B-36A84397D079}">
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:T224"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="43.85546875" customWidth="1"/>
-    <col min="2" max="2" width="43.42578125" customWidth="1"/>
+    <col min="1" max="1" width="43.88671875" customWidth="1"/>
+    <col min="2" max="2" width="43.44140625" customWidth="1"/>
+    <col min="10" max="11" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="7.21875" customWidth="1"/>
+    <col min="13" max="13" width="37" customWidth="1"/>
+    <col min="14" max="14" width="16.77734375" customWidth="1"/>
+    <col min="15" max="15" width="10.5546875" customWidth="1"/>
+    <col min="16" max="16" width="11.21875" customWidth="1"/>
+    <col min="17" max="17" width="9.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:17">
       <c r="A1" s="2" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:17">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
+      <c r="A5" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
+      <c r="A6" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
+      <c r="A8" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
+      <c r="A9" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
+      <c r="A10" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="M10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="O10" s="4">
+        <v>4</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q10" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M11" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B5" s="2" t="s">
+      <c r="N11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O11" s="4">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17">
+      <c r="A12" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="O12" s="2">
+        <v>6</v>
+      </c>
+      <c r="P12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q12" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
+      <c r="A13" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O13" s="2">
+        <v>6</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q13" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
+      <c r="A14" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" s="2">
+        <v>6</v>
+      </c>
+      <c r="P14" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17">
+      <c r="A15" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="O15" s="2">
+        <v>8</v>
+      </c>
+      <c r="P15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q15" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17">
+      <c r="A16" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="O16" s="2">
+        <v>6</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17">
+      <c r="A17" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="O17" s="2">
+        <v>5</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17">
+      <c r="A18" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" s="2">
+        <v>5</v>
+      </c>
+      <c r="P18" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q18" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17">
+      <c r="A19" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" s="2">
+        <v>5</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q19" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17">
+      <c r="A20" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O20" s="2">
+        <v>5</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q20" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17">
+      <c r="A21" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="N21" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O21" s="2">
+        <v>8</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q21" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17">
+      <c r="A22" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="O22" s="2">
+        <v>7</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q22" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17">
+      <c r="A23" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="O23" s="2">
+        <v>7</v>
+      </c>
+      <c r="P23" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q23" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17">
+      <c r="A24" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="O24" s="2">
+        <v>7</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17">
+      <c r="A25" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O25" s="2">
+        <v>7</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q25" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
+      <c r="A26" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="O26" s="2">
+        <v>7</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q26" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17">
+      <c r="A27" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
+      <c r="M27" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O27" s="2">
+        <v>7</v>
+      </c>
+      <c r="P27" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q27" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17">
       <c r="A28" s="1" t="s">
-        <v>201</v>
+        <v>149</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
+        <v>66</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O28" s="2">
+        <v>8</v>
+      </c>
+      <c r="P28" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q28" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17">
       <c r="A29" s="1" t="s">
-        <v>202</v>
+        <v>149</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
+        <v>75</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="O29" s="2">
+        <v>5</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q29" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17">
       <c r="A30" s="1" t="s">
-        <v>203</v>
+        <v>149</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
+        <v>85</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O30" s="2">
+        <v>5</v>
+      </c>
+      <c r="P30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q30" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17">
       <c r="A31" s="1" t="s">
-        <v>204</v>
+        <v>149</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
+        <v>72</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31" s="2">
+        <v>5</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q31" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17">
       <c r="A32" s="1" t="s">
-        <v>205</v>
+        <v>149</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
+        <v>70</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O32" s="2">
+        <v>5</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q32" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17">
       <c r="A33" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
+        <v>150</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O33" s="2">
+        <v>5</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q33" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17">
       <c r="A34" s="1" t="s">
-        <v>207</v>
+        <v>150</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
+        <v>66</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="O34" s="2">
+        <v>5</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q34" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17">
       <c r="A35" s="1" t="s">
-        <v>208</v>
+        <v>150</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
+        <v>76</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="O35" s="2">
+        <v>5</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q35" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17">
       <c r="A36" s="1" t="s">
-        <v>209</v>
+        <v>150</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
+        <v>69</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="O36" s="2">
+        <v>5</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q36" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17">
       <c r="A37" s="1" t="s">
-        <v>210</v>
+        <v>150</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
+        <v>97</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O37" s="2">
+        <v>5</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17">
       <c r="A38" s="1" t="s">
-        <v>211</v>
+        <v>150</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
+        <v>396</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O38" s="2">
+        <v>5</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q38" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17">
       <c r="A39" s="1" t="s">
-        <v>212</v>
+        <v>151</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="40" spans="1:2">
+      <c r="M39" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="O39" s="2">
+        <v>5</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q39" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17">
       <c r="A40" s="1" t="s">
-        <v>213</v>
+        <v>151</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O40" s="2">
+        <v>5</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q40" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17">
+      <c r="A41" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O41" s="2">
+        <v>5</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q41" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17">
+      <c r="A42" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="O42" s="2">
+        <v>5</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q42" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17">
+      <c r="A43" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="O43" s="2">
+        <v>5</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q43" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17">
+      <c r="A44" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="N44" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="O44" s="2">
+        <v>5</v>
+      </c>
+      <c r="P44" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q44" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17">
+      <c r="A45" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="O45" s="2">
+        <v>5</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q45" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17">
+      <c r="A46" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O46" s="2">
+        <v>5</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q46" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17">
+      <c r="A47" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="N47" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="O47" s="15">
+        <v>5</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q47" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17">
+      <c r="A48" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20">
+      <c r="A49" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20">
+      <c r="A50" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20">
+      <c r="A51" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20">
+      <c r="A52" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20">
+      <c r="A53" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M53" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="O53" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="P53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S53" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="T53" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20">
+      <c r="A54" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="M54" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P54" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S54" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T54" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20">
+      <c r="A55" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M55" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="N55" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="O55" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P55" s="1">
+        <v>38</v>
+      </c>
+      <c r="Q55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S55" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T55" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20">
+      <c r="A56" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="O56" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P56" s="1">
+        <v>42</v>
+      </c>
+      <c r="Q56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S56" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T56" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20">
+      <c r="A57" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M57" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="N57" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="O57" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P57" s="1">
+        <v>38</v>
+      </c>
+      <c r="Q57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S57" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T57" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20">
+      <c r="A58" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M58" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="N58" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="O58" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P58" s="1">
+        <v>41</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S58" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T58" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20">
+      <c r="A59" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="O59" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P59" s="1">
+        <v>44</v>
+      </c>
+      <c r="Q59" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S59" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T59" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20">
+      <c r="A60" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M60" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P60" s="1">
+        <v>44</v>
+      </c>
+      <c r="Q60" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S60" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T60" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20">
+      <c r="A61" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="O61" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P61" s="1">
+        <v>40</v>
+      </c>
+      <c r="Q61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R61" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S61" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T61" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20">
+      <c r="A62" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="O62" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P62" s="1">
+        <v>42</v>
+      </c>
+      <c r="Q62" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S62" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T62" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20">
+      <c r="A63" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B41" s="2" t="s">
+      <c r="M63" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="O63" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P63" s="1">
+        <v>43</v>
+      </c>
+      <c r="Q63" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S63" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T63" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20">
+      <c r="A64" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="N64" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="O64" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P64" s="1">
+        <v>44</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S64" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T64" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20">
+      <c r="A65" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M65" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="N65" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="O65" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P65" s="1">
+        <v>38</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S65" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T65" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20">
+      <c r="A66" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M66" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N66" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="O66" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P66" s="1">
+        <v>40</v>
+      </c>
+      <c r="Q66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S66" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T66" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20">
+      <c r="A67" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="O67" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P67" s="1">
+        <v>40</v>
+      </c>
+      <c r="Q67" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S67" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T67" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20">
+      <c r="A68" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B68" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="B42" s="2" t="s">
+      <c r="M68" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="N68" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="O68" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P68" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q68" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S68" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T68" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20">
+      <c r="A69" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M69" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="O69" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P69" s="1">
+        <v>38</v>
+      </c>
+      <c r="Q69" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S69" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T69" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20">
+      <c r="A70" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M70" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="N70" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="O70" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P70" s="1">
+        <v>42</v>
+      </c>
+      <c r="Q70" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S70" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T70" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20">
+      <c r="A71" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="O71" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P71" s="1">
+        <v>40</v>
+      </c>
+      <c r="Q71" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S71" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T71" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20">
+      <c r="A72" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M72" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="O72" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P72" s="1">
+        <v>44</v>
+      </c>
+      <c r="Q72" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S72" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T72" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20">
+      <c r="A73" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M73" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="N73" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="O73" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P73" s="1">
+        <v>41</v>
+      </c>
+      <c r="Q73" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S73" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T73" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20">
+      <c r="A74" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B74" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="B43" s="2" t="s">
+      <c r="M74" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="O74" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P74" s="1">
+        <v>44</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S74" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T74" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20">
+      <c r="A75" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M75" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="N75" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="O75" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P75" s="1">
+        <v>42</v>
+      </c>
+      <c r="Q75" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S75" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T75" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20">
+      <c r="A76" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="N76" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="O76" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P76" s="1">
+        <v>44</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S76" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T76" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20">
+      <c r="A77" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M77" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="N77" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="O77" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P77" s="1">
+        <v>40</v>
+      </c>
+      <c r="Q77" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S77" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T77" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="78" spans="1:20">
+      <c r="A78" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M78" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="N78" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="O78" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P78" s="1">
+        <v>42</v>
+      </c>
+      <c r="Q78" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S78" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T78" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20">
+      <c r="A79" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B44" s="2" t="s">
+      <c r="M79" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="N79" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="O79" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P79" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q79" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S79" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="T79" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="80" spans="1:20">
+      <c r="A80" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="O80" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P80" s="1">
+        <v>44</v>
+      </c>
+      <c r="Q80" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S80" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T80" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="81" spans="1:20">
+      <c r="A81" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="O81" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P81" s="1">
+        <v>38</v>
+      </c>
+      <c r="Q81" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S81" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T81" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="82" spans="1:20">
+      <c r="A82" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M82" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="O82" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P82" s="1">
+        <v>42</v>
+      </c>
+      <c r="Q82" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R82" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S82" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T82" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="83" spans="1:20">
+      <c r="A83" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="B45" s="2" t="s">
+      <c r="M83" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="N83" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="O83" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P83" s="1">
+        <v>38</v>
+      </c>
+      <c r="Q83" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S83" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T83" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="84" spans="1:20">
+      <c r="A84" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="O84" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P84" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q84" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S84" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T84" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="85" spans="1:20">
+      <c r="A85" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="M85" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="N85" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="O85" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P85" s="1">
+        <v>30</v>
+      </c>
+      <c r="Q85" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R85" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S85" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T85" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="86" spans="1:20">
+      <c r="A86" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="M86" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="N86" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="O86" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P86" s="1">
+        <v>45</v>
+      </c>
+      <c r="Q86" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R86" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S86" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="T86" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="87" spans="1:20">
+      <c r="A87" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="O87" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P87" s="1">
+        <v>22</v>
+      </c>
+      <c r="Q87" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R87" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S87" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="T87" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="88" spans="1:20">
+      <c r="A88" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M88" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="N88" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="O88" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P88" s="1">
+        <v>32</v>
+      </c>
+      <c r="Q88" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S88" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="T88" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="89" spans="1:20">
+      <c r="A89" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M89" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="N89" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="O89" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P89" s="1">
+        <v>35</v>
+      </c>
+      <c r="Q89" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R89" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S89" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="T89" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="90" spans="1:20">
+      <c r="A90" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M90" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="N90" s="1" t="s">
+        <v>330</v>
+      </c>
+      <c r="O90" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P90" s="1">
+        <v>32</v>
+      </c>
+      <c r="Q90" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R90" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S90" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="T90" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="91" spans="1:20">
+      <c r="A91" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="O91" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P91" s="1">
+        <v>32</v>
+      </c>
+      <c r="Q91" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R91" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S91" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="T91" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="92" spans="1:20">
+      <c r="A92" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M92" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="N92" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="O92" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P92" s="1">
+        <v>34</v>
+      </c>
+      <c r="Q92" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S92" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="T92" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="93" spans="1:20">
+      <c r="A93" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="M93" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="N93" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="O93" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="P93" s="1">
+        <v>34</v>
+      </c>
+      <c r="Q93" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R93" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S93" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="T93" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="94" spans="1:20">
+      <c r="A94" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="O94" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P94" s="1">
+        <v>16</v>
+      </c>
+      <c r="Q94" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R94" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S94" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="T94" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="95" spans="1:20">
+      <c r="A95" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="N95" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="O95" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P95" s="1">
+        <v>9</v>
+      </c>
+      <c r="Q95" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R95" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S95" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T95" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="96" spans="1:20">
+      <c r="A96" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="N96" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="O96" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P96" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q96" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R96" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S96" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="T96" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="97" spans="1:20">
+      <c r="A97" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="O97" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P97" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q97" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R97" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S97" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T97" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="98" spans="1:20">
+      <c r="A98" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="N98" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="O98" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P98" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q98" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R98" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S98" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T98" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="99" spans="1:20">
+      <c r="A99" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="N99" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="O99" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P99" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q99" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R99" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S99" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T99" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="100" spans="1:20">
+      <c r="A100" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="N100" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="O100" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P100" s="1">
+        <v>7</v>
+      </c>
+      <c r="Q100" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R100" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S100" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T100" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="101" spans="1:20">
+      <c r="A101" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="N101" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="O101" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P101" s="1">
+        <v>13</v>
+      </c>
+      <c r="Q101" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R101" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S101" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="T101" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="102" spans="1:20">
+      <c r="A102" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="M102" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="N102" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="O102" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="P102" s="13">
+        <v>15</v>
+      </c>
+      <c r="Q102" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="R102" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="S102" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="T102" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="103" spans="1:20">
+      <c r="A103" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M103" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="N103" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="O103" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P103" s="12">
+        <v>16</v>
+      </c>
+      <c r="Q103" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R103" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S103" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="T103" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="104" spans="1:20">
+      <c r="A104" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="M104" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="N104" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="O104" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P104" s="12">
+        <v>15</v>
+      </c>
+      <c r="Q104" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R104" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S104" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="T104" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="105" spans="1:20">
+      <c r="A105" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B105" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B46" s="2" t="s">
+      <c r="M105" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="N105" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="O105" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P105" s="12">
+        <v>18</v>
+      </c>
+      <c r="Q105" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R105" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S105" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="T105" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="106" spans="1:20">
+      <c r="A106" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M106" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="N106" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="O106" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P106" s="12">
+        <v>18</v>
+      </c>
+      <c r="Q106" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R106" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S106" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="T106" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="107" spans="1:20">
+      <c r="A107" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M107" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="N107" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="O107" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P107" s="12">
         <v>12</v>
       </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="B47" s="2" t="s">
+      <c r="Q107" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R107" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S107" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="T107" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="108" spans="1:20">
+      <c r="A108" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M108" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="N108" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="O108" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P108" s="12">
         <v>12</v>
       </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B48" s="2" t="s">
+      <c r="Q108" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R108" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S108" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="T108" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="109" spans="1:20">
+      <c r="A109" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M109" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="N109" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="O109" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P109" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q109" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R109" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S109" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T109" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="110" spans="1:20">
+      <c r="A110" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="M110" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="N110" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="O110" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P110" s="12">
         <v>12</v>
       </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B49" s="2" t="s">
+      <c r="Q110" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R110" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S110" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T110" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="111" spans="1:20">
+      <c r="A111" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B50" s="2" t="s">
+      <c r="M111" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="N111" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="O111" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P111" s="12">
+        <v>7</v>
+      </c>
+      <c r="Q111" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R111" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S111" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T111" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="112" spans="1:20">
+      <c r="A112" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M112" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="N112" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="O112" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P112" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q112" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R112" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S112" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T112" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20">
+      <c r="A113" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M113" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="N113" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="O113" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P113" s="12">
         <v>12</v>
+      </c>
+      <c r="Q113" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R113" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S113" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="T113" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20">
+      <c r="A114" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="M114" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="N114" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="O114" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P114" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q114" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R114" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S114" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T114" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20">
+      <c r="A115" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="M115" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="N115" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="O115" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P115" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q115" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R115" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S115" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T115" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:20">
+      <c r="A116" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="M116" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="N116" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="O116" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P116" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q116" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R116" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S116" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T116" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20">
+      <c r="A117" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M117" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="N117" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="O117" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P117" s="12">
+        <v>7</v>
+      </c>
+      <c r="Q117" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R117" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S117" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T117" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20">
+      <c r="A118" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M118" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="N118" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="O118" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P118" s="12">
+        <v>20</v>
+      </c>
+      <c r="Q118" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R118" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S118" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T118" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20">
+      <c r="A119" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M119" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="N119" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P119" s="12">
+        <v>18</v>
+      </c>
+      <c r="Q119" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R119" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S119" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T119" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20">
+      <c r="A120" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="M120" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="N120" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="O120" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P120" s="12">
+        <v>6</v>
+      </c>
+      <c r="Q120" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R120" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S120" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T120" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20">
+      <c r="A121" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M121" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="N121" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="P121" s="12">
+        <v>6</v>
+      </c>
+      <c r="Q121" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R121" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S121" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="T121" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="122" spans="1:20">
+      <c r="A122" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M122" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="N122" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="O122" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="P122" s="12">
+        <v>36</v>
+      </c>
+      <c r="Q122" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R122" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S122" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T122" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="123" spans="1:20">
+      <c r="A123" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M123" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="N123" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="O123" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="P123" s="12">
+        <v>38</v>
+      </c>
+      <c r="Q123" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R123" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S123" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T123" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="124" spans="1:20">
+      <c r="A124" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="M124" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="N124" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="O124" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="P124" s="12">
+        <v>40</v>
+      </c>
+      <c r="Q124" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R124" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S124" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T124" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="125" spans="1:20">
+      <c r="A125" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M125" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="N125" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="O125" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="P125" s="12">
+        <v>38</v>
+      </c>
+      <c r="Q125" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R125" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S125" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T125" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="126" spans="1:20">
+      <c r="A126" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="M126" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="N126" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="O126" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="P126" s="12">
+        <v>40</v>
+      </c>
+      <c r="Q126" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R126" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S126" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T126" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="127" spans="1:20">
+      <c r="A127" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="M127" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="N127" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="O127" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="P127" s="12">
+        <v>39</v>
+      </c>
+      <c r="Q127" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R127" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S127" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="T127" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="128" spans="1:20">
+      <c r="A128" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="M128" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="N128" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="O128" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P128" s="12">
+        <v>10</v>
+      </c>
+      <c r="Q128" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R128" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S128" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="T128" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="129" spans="1:20">
+      <c r="A129" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="M129" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="N129" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="O129" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P129" s="12">
+        <v>12</v>
+      </c>
+      <c r="Q129" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="R129" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="S129" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="T129" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="130" spans="1:20">
+      <c r="A130" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="131" spans="1:20">
+      <c r="A131" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="132" spans="1:20">
+      <c r="A132" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="133" spans="1:20">
+      <c r="A133" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="134" spans="1:20">
+      <c r="A134" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="135" spans="1:20">
+      <c r="A135" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="136" spans="1:20">
+      <c r="A136" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="137" spans="1:20">
+      <c r="A137" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="138" spans="1:20">
+      <c r="A138" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="139" spans="1:20">
+      <c r="A139" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="140" spans="1:20">
+      <c r="A140" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="141" spans="1:20">
+      <c r="A141" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="142" spans="1:20">
+      <c r="A142" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="143" spans="1:20">
+      <c r="A143" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="144" spans="1:20">
+      <c r="A144" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2">
+      <c r="A182" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2">
+      <c r="A183" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2">
+      <c r="A184" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2">
+      <c r="A185" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2">
+      <c r="A186" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2">
+      <c r="A187" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2">
+      <c r="A188" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2">
+      <c r="A189" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2">
+      <c r="A190" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2">
+      <c r="A191" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2">
+      <c r="A192" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2">
+      <c r="A193" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2">
+      <c r="A194" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2">
+      <c r="A195" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2">
+      <c r="A196" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2">
+      <c r="A197" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2">
+      <c r="A198" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2">
+      <c r="A199" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2">
+      <c r="A200" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2">
+      <c r="A201" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2">
+      <c r="A202" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2">
+      <c r="A203" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2">
+      <c r="A204" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2">
+      <c r="A205" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2">
+      <c r="A206" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2">
+      <c r="A207" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2">
+      <c r="A208" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2">
+      <c r="A209" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2">
+      <c r="A210" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2">
+      <c r="A211" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2">
+      <c r="A212" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2">
+      <c r="A213" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2">
+      <c r="A214" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2">
+      <c r="A215" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2">
+      <c r="A216" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2">
+      <c r="A217" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2">
+      <c r="A218" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2">
+      <c r="A219" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2">
+      <c r="A220" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2">
+      <c r="A221" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2">
+      <c r="A222" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2">
+      <c r="A223" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2">
+      <c r="A224" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -2117,11 +6160,11 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17577034-6810-45EB-B138-D5219A90AFAB}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="11.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -2140,10 +6183,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>324</v>
+        <v>288</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>64</v>
@@ -2154,10 +6197,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>320</v>
+        <v>284</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>325</v>
+        <v>289</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>64</v>
@@ -2168,10 +6211,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>321</v>
+        <v>285</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>64</v>
@@ -2182,10 +6225,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>64</v>
@@ -2196,10 +6239,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>335</v>
+        <v>299</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>64</v>
@@ -2215,19 +6258,19 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF68DE72-AEE1-4ED0-BFF5-DFC6E78C7F67}">
-  <dimension ref="A1:B38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B39"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="40.5703125" customWidth="1"/>
-    <col min="2" max="2" width="36.85546875" customWidth="1"/>
+    <col min="1" max="1" width="40.5546875" customWidth="1"/>
+    <col min="2" max="2" width="36.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
-        <v>234</v>
+        <v>198</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>305</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -2235,7 +6278,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -2243,7 +6286,7 @@
         <v>12</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -2251,7 +6294,7 @@
         <v>66</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>278</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -2259,7 +6302,7 @@
         <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -2267,7 +6310,7 @@
         <v>68</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -2275,7 +6318,7 @@
         <v>69</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -2283,7 +6326,7 @@
         <v>70</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -2291,7 +6334,7 @@
         <v>71</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -2299,7 +6342,7 @@
         <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -2307,7 +6350,7 @@
         <v>73</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>311</v>
+        <v>275</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -2315,7 +6358,7 @@
         <v>74</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -2323,7 +6366,7 @@
         <v>75</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -2331,7 +6374,7 @@
         <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -2339,7 +6382,7 @@
         <v>77</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -2347,7 +6390,7 @@
         <v>78</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -2355,7 +6398,7 @@
         <v>79</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -2363,7 +6406,7 @@
         <v>80</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -2371,7 +6414,7 @@
         <v>81</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>314</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -2379,7 +6422,7 @@
         <v>82</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>315</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -2387,7 +6430,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>316</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -2395,7 +6438,7 @@
         <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>317</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -2403,7 +6446,7 @@
         <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>318</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -2411,7 +6454,7 @@
         <v>86</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -2419,7 +6462,7 @@
         <v>87</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -2427,7 +6470,7 @@
         <v>88</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -2435,7 +6478,7 @@
         <v>89</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -2443,7 +6486,7 @@
         <v>90</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -2451,7 +6494,7 @@
         <v>91</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -2459,7 +6502,7 @@
         <v>92</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>310</v>
+        <v>274</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -2467,7 +6510,7 @@
         <v>93</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>311</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -2475,7 +6518,7 @@
         <v>94</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>312</v>
+        <v>276</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -2483,7 +6526,7 @@
         <v>95</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>313</v>
+        <v>277</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -2491,7 +6534,7 @@
         <v>96</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -2499,7 +6542,7 @@
         <v>97</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>306</v>
+        <v>270</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -2507,7 +6550,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -2515,7 +6558,7 @@
         <v>99</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>308</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -2523,7 +6566,15 @@
         <v>100</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>309</v>
+        <v>273</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -2534,17 +6585,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89F0278-9583-4842-A27E-70B7F705F4F8}">
-  <dimension ref="A1:H38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.42578125" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18.140625" customWidth="1"/>
-    <col min="6" max="6" width="23.7109375" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" customWidth="1"/>
+    <col min="5" max="5" width="18.109375" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="55.85546875" customWidth="1"/>
+    <col min="8" max="8" width="55.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3199,6 +7250,23 @@
         <v>64</v>
       </c>
       <c r="E38" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="C39" s="15">
+        <v>5</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3211,11 +7279,11 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D70A01-E011-4D5C-AF4A-BF7940E4CD9E}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="38.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.85546875" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="38.5546875" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3367,13 +7435,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7799660A-6A70-4E53-ADA2-AEC7FFF55C28}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" customWidth="1"/>
-    <col min="2" max="2" width="14.5703125" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" customWidth="1"/>
-    <col min="4" max="4" width="9.5703125" customWidth="1"/>
-    <col min="5" max="5" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="36.5546875" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" customWidth="1"/>
+    <col min="4" max="4" width="9.5546875" customWidth="1"/>
+    <col min="5" max="5" width="34.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3536,16 +7604,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2111D6-4486-49FF-8151-BCB73604576D}">
-  <dimension ref="A1:H50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:H77"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="37.85546875" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" customWidth="1"/>
-    <col min="3" max="3" width="33.42578125" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" customWidth="1"/>
-    <col min="6" max="6" width="9.85546875" customWidth="1"/>
-    <col min="7" max="7" width="36.7109375" customWidth="1"/>
-    <col min="8" max="8" width="35.85546875" customWidth="1"/>
+    <col min="1" max="1" width="37.88671875" customWidth="1"/>
+    <col min="2" max="2" width="25.44140625" customWidth="1"/>
+    <col min="3" max="3" width="33.44140625" customWidth="1"/>
+    <col min="5" max="5" width="9.44140625" customWidth="1"/>
+    <col min="6" max="6" width="9.88671875" customWidth="1"/>
+    <col min="7" max="7" width="36.6640625" customWidth="1"/>
+    <col min="8" max="8" width="35.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -3576,13 +7644,13 @@
     </row>
     <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D2" s="1">
         <v>30</v>
@@ -3602,13 +7670,13 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>139</v>
+        <v>315</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D3" s="1">
         <v>38</v>
@@ -3628,13 +7696,13 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>177</v>
+        <v>146</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>140</v>
+        <v>301</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D4" s="1">
         <v>42</v>
@@ -3654,13 +7722,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>141</v>
+        <v>324</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D5" s="1">
         <v>38</v>
@@ -3680,13 +7748,13 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>179</v>
+        <v>148</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>142</v>
+        <v>325</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D6" s="1">
         <v>41</v>
@@ -3706,13 +7774,13 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>180</v>
+        <v>149</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>143</v>
+        <v>302</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D7" s="1">
         <v>44</v>
@@ -3732,13 +7800,13 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>181</v>
+        <v>150</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>144</v>
+        <v>316</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D8" s="1">
         <v>44</v>
@@ -3758,13 +7826,13 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>145</v>
+        <v>303</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D9" s="1">
         <v>40</v>
@@ -3784,13 +7852,13 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>183</v>
+        <v>152</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>146</v>
+        <v>326</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D10" s="1">
         <v>42</v>
@@ -3810,13 +7878,13 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>184</v>
+        <v>153</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>147</v>
+        <v>327</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D11" s="1">
         <v>43</v>
@@ -3836,13 +7904,13 @@
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>216</v>
       </c>
       <c r="D12" s="1">
         <v>44</v>
@@ -3862,13 +7930,13 @@
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>149</v>
+        <v>304</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D13" s="1">
         <v>38</v>
@@ -3888,13 +7956,13 @@
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>150</v>
+        <v>305</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D14" s="1">
         <v>40</v>
@@ -3914,13 +7982,13 @@
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>188</v>
+        <v>157</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>151</v>
+        <v>306</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D15" s="1">
         <v>40</v>
@@ -3940,13 +8008,13 @@
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>152</v>
+        <v>307</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D16" s="1">
         <v>35</v>
@@ -3966,13 +8034,13 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="1" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>153</v>
+        <v>308</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D17" s="1">
         <v>38</v>
@@ -3992,13 +8060,13 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>154</v>
+        <v>317</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D18" s="1">
         <v>42</v>
@@ -4018,13 +8086,13 @@
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>155</v>
+        <v>318</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D19" s="1">
         <v>40</v>
@@ -4044,13 +8112,13 @@
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>156</v>
+        <v>319</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D20" s="1">
         <v>44</v>
@@ -4070,13 +8138,13 @@
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>194</v>
+        <v>163</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>157</v>
+        <v>309</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D21" s="1">
         <v>41</v>
@@ -4096,13 +8164,13 @@
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>158</v>
+        <v>310</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D22" s="1">
         <v>44</v>
@@ -4122,13 +8190,13 @@
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>159</v>
+        <v>320</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D23" s="1">
         <v>42</v>
@@ -4148,13 +8216,13 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>160</v>
+        <v>311</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D24" s="1">
         <v>44</v>
@@ -4174,13 +8242,13 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="1" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>161</v>
+        <v>321</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D25" s="1">
         <v>40</v>
@@ -4200,13 +8268,13 @@
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="1" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>162</v>
+        <v>312</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D26" s="1">
         <v>42</v>
@@ -4226,16 +8294,16 @@
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="1" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>163</v>
+        <v>335</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="D27" s="1">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>64</v>
@@ -4243,22 +8311,22 @@
       <c r="F27" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>130</v>
+      <c r="G27" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>164</v>
+        <v>322</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D28" s="1">
         <v>44</v>
@@ -4278,13 +8346,13 @@
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>165</v>
+        <v>313</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D29" s="1">
         <v>38</v>
@@ -4304,13 +8372,13 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>166</v>
+        <v>329</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D30" s="1">
         <v>42</v>
@@ -4330,13 +8398,13 @@
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>167</v>
+        <v>314</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D31" s="1">
         <v>38</v>
@@ -4356,13 +8424,13 @@
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>168</v>
+        <v>323</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D32" s="1">
         <v>30</v>
@@ -4382,13 +8450,13 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D33" s="1">
         <v>30</v>
@@ -4408,13 +8476,13 @@
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D34" s="1">
         <v>45</v>
@@ -4434,13 +8502,13 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D35" s="1">
         <v>22</v>
@@ -4455,18 +8523,18 @@
         <v>101</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="1" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D36" s="1">
         <v>32</v>
@@ -4481,18 +8549,18 @@
         <v>101</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="1" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D37" s="1">
         <v>35</v>
@@ -4507,18 +8575,18 @@
         <v>101</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>138</v>
+        <v>330</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D38" s="1">
         <v>32</v>
@@ -4533,18 +8601,18 @@
         <v>111</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>139</v>
+        <v>331</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D39" s="1">
         <v>32</v>
@@ -4559,18 +8627,18 @@
         <v>111</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="1" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>138</v>
+        <v>332</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D40" s="1">
         <v>34</v>
@@ -4585,18 +8653,18 @@
         <v>112</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="1" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>139</v>
+        <v>333</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="D41" s="1">
         <v>34</v>
@@ -4611,21 +8679,21 @@
         <v>112</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="1" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>140</v>
+        <v>334</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="D42" s="1">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>64</v>
@@ -4633,22 +8701,22 @@
       <c r="F42" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>174</v>
+      <c r="G42" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="2" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="D43" s="1">
         <v>9</v>
@@ -4668,13 +8736,13 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>224</v>
+        <v>367</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="D44" s="1">
         <v>14</v>
@@ -4694,13 +8762,13 @@
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="2" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>225</v>
+        <v>348</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="D45" s="1">
         <v>7</v>
@@ -4720,13 +8788,13 @@
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="2" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>226</v>
+        <v>350</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="D46" s="1">
         <v>8</v>
@@ -4746,13 +8814,13 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="2" t="s">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>227</v>
+        <v>193</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="D47" s="1">
         <v>7</v>
@@ -4772,13 +8840,13 @@
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="2" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>228</v>
+        <v>194</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="D48" s="1">
         <v>7</v>
@@ -4798,13 +8866,13 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="2" t="s">
-        <v>231</v>
+        <v>195</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>229</v>
+        <v>336</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="D49" s="1">
         <v>13</v>
@@ -4818,34 +8886,736 @@
       <c r="G49" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="H49" s="1" t="s">
-        <v>174</v>
+      <c r="H49" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="50" spans="1:8">
-      <c r="A50" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="D50" s="1">
+      <c r="A50" s="14" t="s">
+        <v>196</v>
+      </c>
+      <c r="B50" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D50" s="13">
         <v>15</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G50" s="2" t="s">
+      <c r="E50" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="F50" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="G50" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="H50" s="1" t="s">
-        <v>174</v>
+      <c r="H50" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B51" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D51" s="12">
+        <v>16</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G51" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B52" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D52" s="12">
+        <v>15</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G52" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B53" s="12" t="s">
+        <v>340</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D53" s="12">
+        <v>18</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G53" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>341</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D54" s="12">
+        <v>18</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B55" s="12" t="s">
+        <v>342</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D55" s="12">
+        <v>12</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B56" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D56" s="12">
+        <v>12</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>344</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D57" s="12">
+        <v>10</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H57" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B58" s="12" t="s">
+        <v>345</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D58" s="12">
+        <v>12</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B59" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D59" s="12">
+        <v>7</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B60" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D60" s="12">
+        <v>10</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D61" s="12">
+        <v>12</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D62" s="12">
+        <v>10</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B63" s="12" t="s">
+        <v>363</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D63" s="12">
+        <v>10</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D64" s="12">
+        <v>10</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B65" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D65" s="12">
+        <v>7</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="B66" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D66" s="12">
+        <v>20</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F66" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>354</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D67" s="12">
+        <v>18</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B68" s="12" t="s">
+        <v>355</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D68" s="12">
+        <v>6</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F68" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B69" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D69" s="12">
+        <v>6</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>357</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D70" s="12">
+        <v>36</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H70" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B71" s="12" t="s">
+        <v>358</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D71" s="12">
+        <v>38</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F71" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H71" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B72" s="12" t="s">
+        <v>359</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D72" s="12">
+        <v>40</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H72" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B73" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D73" s="12">
+        <v>38</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F73" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H73" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B74" s="12" t="s">
+        <v>361</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D74" s="12">
+        <v>40</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F74" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B75" s="12" t="s">
+        <v>362</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="D75" s="12">
+        <v>39</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H75" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B76" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D76" s="12">
+        <v>10</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D77" s="12">
+        <v>12</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -4857,14 +9627,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256B2A91-27AB-4BC1-A1F0-115B786A674D}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="37.140625" customWidth="1"/>
+    <col min="1" max="1" width="37.109375" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" customWidth="1"/>
-    <col min="7" max="7" width="38.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="15.44140625" customWidth="1"/>
+    <col min="7" max="7" width="38.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -4875,7 +9645,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>235</v>
+        <v>199</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>2</v>
@@ -4884,18 +9654,18 @@
         <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>328</v>
+        <v>292</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>237</v>
+        <v>201</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>241</v>
+        <v>205</v>
       </c>
       <c r="C2" s="2">
         <v>8</v>
@@ -4907,18 +9677,18 @@
         <v>65</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>300</v>
+        <v>264</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>242</v>
+        <v>206</v>
       </c>
       <c r="C3" s="2">
         <v>6</v>
@@ -4930,18 +9700,18 @@
         <v>65</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="2" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>243</v>
+        <v>207</v>
       </c>
       <c r="C4" s="2">
         <v>2</v>
@@ -4953,18 +9723,18 @@
         <v>65</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
-        <v>240</v>
+        <v>204</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>244</v>
+        <v>208</v>
       </c>
       <c r="C5" s="2">
         <v>2</v>
@@ -4976,18 +9746,18 @@
         <v>65</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
-        <v>260</v>
+        <v>224</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>245</v>
+        <v>209</v>
       </c>
       <c r="C6" s="2">
         <v>4</v>
@@ -4999,18 +9769,18 @@
         <v>65</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>320</v>
+        <v>284</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="2" t="s">
-        <v>261</v>
+        <v>225</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="C7" s="2">
         <v>4</v>
@@ -5022,18 +9792,18 @@
         <v>65</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>320</v>
+        <v>284</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>262</v>
+        <v>226</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>247</v>
+        <v>211</v>
       </c>
       <c r="C8" s="2">
         <v>2</v>
@@ -5045,18 +9815,18 @@
         <v>65</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>320</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>263</v>
+        <v>227</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="C9" s="2">
         <v>2</v>
@@ -5068,18 +9838,18 @@
         <v>65</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>320</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>264</v>
+        <v>228</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="C10" s="2">
         <v>4</v>
@@ -5091,18 +9861,18 @@
         <v>65</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>265</v>
+        <v>229</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>250</v>
+        <v>214</v>
       </c>
       <c r="C11" s="2">
         <v>4</v>
@@ -5114,18 +9884,18 @@
         <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
-        <v>266</v>
+        <v>230</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>251</v>
+        <v>215</v>
       </c>
       <c r="C12" s="2">
         <v>2</v>
@@ -5137,18 +9907,18 @@
         <v>65</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
-        <v>267</v>
+        <v>231</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>252</v>
+        <v>216</v>
       </c>
       <c r="C13" s="2">
         <v>6</v>
@@ -5160,18 +9930,18 @@
         <v>65</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>322</v>
+        <v>286</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="2" t="s">
-        <v>268</v>
+        <v>232</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>253</v>
+        <v>217</v>
       </c>
       <c r="C14" s="2">
         <v>4</v>
@@ -5183,18 +9953,18 @@
         <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
-        <v>269</v>
+        <v>233</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>254</v>
+        <v>218</v>
       </c>
       <c r="C15" s="2">
         <v>4</v>
@@ -5206,18 +9976,18 @@
         <v>65</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="2" t="s">
-        <v>270</v>
+        <v>234</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>255</v>
+        <v>219</v>
       </c>
       <c r="C16" s="2">
         <v>4</v>
@@ -5229,18 +9999,18 @@
         <v>65</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="2" t="s">
-        <v>271</v>
+        <v>235</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>256</v>
+        <v>220</v>
       </c>
       <c r="C17" s="2">
         <v>6</v>
@@ -5252,18 +10022,18 @@
         <v>65</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="2" t="s">
-        <v>272</v>
+        <v>236</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>257</v>
+        <v>221</v>
       </c>
       <c r="C18" s="2">
         <v>6</v>
@@ -5275,18 +10045,18 @@
         <v>65</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="2" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>258</v>
+        <v>222</v>
       </c>
       <c r="C19" s="2">
         <v>8</v>
@@ -5298,18 +10068,18 @@
         <v>65</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>323</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2" t="s">
-        <v>332</v>
+        <v>296</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="C20" s="2">
         <v>4</v>
@@ -5321,18 +10091,18 @@
         <v>65</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>321</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>330</v>
+        <v>294</v>
       </c>
       <c r="C21" s="2">
         <v>4</v>
@@ -5344,18 +10114,18 @@
         <v>65</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>321</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>334</v>
+        <v>298</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>331</v>
+        <v>295</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
@@ -5367,10 +10137,10 @@
         <v>65</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>259</v>
+        <v>223</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>321</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -5381,9 +10151,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEDC361-D738-4510-89A2-AB67CB12EBDF}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="36.85546875" customWidth="1"/>
+    <col min="1" max="1" width="36.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -5402,7 +10172,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>276</v>
+        <v>240</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>40</v>
@@ -5416,7 +10186,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>29</v>
@@ -5430,10 +10200,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>278</v>
+        <v>242</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>64</v>
@@ -5444,7 +10214,7 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>279</v>
+        <v>243</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -5458,10 +10228,10 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>280</v>
+        <v>244</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>64</v>
@@ -5472,7 +10242,7 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>281</v>
+        <v>245</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>44</v>
@@ -5486,7 +10256,7 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>53</v>
@@ -5506,14 +10276,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F05608C-89F7-443B-8F02-A238CB7CF577}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="38.85546875" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" customWidth="1"/>
+    <col min="1" max="1" width="38.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" customWidth="1"/>
-    <col min="6" max="6" width="11.85546875" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" customWidth="1"/>
+    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="7" max="7" width="36.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5527,27 +10297,27 @@
         <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>283</v>
+        <v>247</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>284</v>
+        <v>248</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>285</v>
+        <v>249</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>286</v>
+        <v>250</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>289</v>
+        <v>253</v>
       </c>
       <c r="B2" s="2">
         <v>123123123</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>287</v>
+        <v>251</v>
       </c>
       <c r="D2" s="10">
         <v>45726.604166666664</v>
@@ -5559,18 +10329,18 @@
         <v>64</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>238</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>290</v>
+        <v>254</v>
       </c>
       <c r="B3" s="2">
         <v>987987987</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>288</v>
+        <v>252</v>
       </c>
       <c r="D3" s="10">
         <v>45726.604166666664</v>
@@ -5582,7 +10352,7 @@
         <v>65</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -5593,12 +10363,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C9E1B61-911D-4E67-9431-CC6DC22C7D98}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="36.5703125" customWidth="1"/>
+    <col min="1" max="1" width="36.5546875" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="6" max="6" width="36.5703125" customWidth="1"/>
-    <col min="7" max="7" width="35.5703125" customWidth="1"/>
+    <col min="6" max="6" width="36.5546875" customWidth="1"/>
+    <col min="7" max="7" width="35.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -5609,24 +10379,24 @@
         <v>24</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>292</v>
+        <v>256</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>236</v>
+        <v>200</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>233</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="2" t="s">
-        <v>294</v>
+        <v>258</v>
       </c>
       <c r="B2" s="2">
         <v>30</v>
@@ -5635,21 +10405,21 @@
         <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>21</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
-        <v>299</v>
+        <v>263</v>
       </c>
       <c r="B3" s="2">
         <v>40</v>
@@ -5658,16 +10428,16 @@
         <v>0</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>293</v>
+        <v>257</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>182</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>

--- a/backend/API/SeedData.xlsx
+++ b/backend/API/SeedData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakub\Desktop\Cs\pc\RestaurantOrderingAppSolution\backend\API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8295F21A-AFD8-4313-9FB9-B37234989A47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E014274-5C7C-4C20-8514-8C45313A6EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-3255" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="4" xr2:uid="{C8CF7BA1-E9AA-4852-A9EB-5F1AD6BFABCB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{C8CF7BA1-E9AA-4852-A9EB-5F1AD6BFABCB}"/>
   </bookViews>
   <sheets>
     <sheet name="CustomerInformation" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2270" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="398">
   <si>
     <t>Id</t>
   </si>
@@ -1237,6 +1237,9 @@
   </si>
   <si>
     <t>5820a2b2-2eb1-4647-87c8-3a77cc77047c</t>
+  </si>
+  <si>
+    <t>SequenceNumber</t>
   </si>
 </sst>
 </file>
@@ -1313,7 +1316,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1348,7 +1351,7 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1357,9 +1360,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normalny" xfId="0" builtinId="0"/>
@@ -1675,16 +1694,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA11DBA6-6284-4357-AB5F-3F63D3FCE544}">
   <dimension ref="A1:H4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="39.44140625" customWidth="1"/>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="22.33203125" customWidth="1"/>
-    <col min="4" max="4" width="15.33203125" customWidth="1"/>
-    <col min="5" max="5" width="26.88671875" customWidth="1"/>
-    <col min="6" max="6" width="21.33203125" customWidth="1"/>
-    <col min="7" max="7" width="32.33203125" customWidth="1"/>
-    <col min="8" max="8" width="36.88671875" customWidth="1"/>
+    <col min="1" max="1" width="39.42578125" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="26.85546875" customWidth="1"/>
+    <col min="6" max="6" width="21.28515625" customWidth="1"/>
+    <col min="7" max="7" width="32.28515625" customWidth="1"/>
+    <col min="8" max="8" width="36.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1778,15 +1797,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4966BB-B585-4EFD-A171-2B6D26A10B97}">
   <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.5546875" customWidth="1"/>
-    <col min="2" max="2" width="23.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" customWidth="1"/>
-    <col min="8" max="8" width="37.44140625" customWidth="1"/>
-    <col min="9" max="9" width="36.44140625" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+    <col min="8" max="8" width="37.42578125" customWidth="1"/>
+    <col min="9" max="9" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -1913,17 +1932,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2E4AC9-0CD2-4F25-AD3B-36A84397D079}">
   <dimension ref="A1:T224"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="43.88671875" customWidth="1"/>
-    <col min="2" max="2" width="43.44140625" customWidth="1"/>
-    <col min="10" max="11" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="7.21875" customWidth="1"/>
-    <col min="13" max="13" width="37" customWidth="1"/>
-    <col min="14" max="14" width="16.77734375" customWidth="1"/>
-    <col min="15" max="15" width="10.5546875" customWidth="1"/>
-    <col min="16" max="16" width="11.21875" customWidth="1"/>
-    <col min="17" max="17" width="9.88671875" customWidth="1"/>
+    <col min="1" max="1" width="43.85546875" customWidth="1"/>
+    <col min="2" max="2" width="43.42578125" customWidth="1"/>
+    <col min="10" max="11" width="8.85546875" customWidth="1"/>
+    <col min="12" max="12" width="7.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" customWidth="1"/>
+    <col min="16" max="16" width="11.28515625" customWidth="1"/>
+    <col min="17" max="17" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -1997,21 +2016,11 @@
       <c r="B9" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="M9" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="1" t="s">
@@ -2020,21 +2029,11 @@
       <c r="B10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M10" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="O10" s="4">
-        <v>4</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q10" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="15"/>
+      <c r="P10" s="12"/>
+      <c r="Q10" s="16"/>
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="1" t="s">
@@ -2043,21 +2042,11 @@
       <c r="B11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="O11" s="4">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q11" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M11" s="12"/>
+      <c r="N11" s="12"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="12"/>
+      <c r="Q11" s="17"/>
     </row>
     <row r="12" spans="1:17">
       <c r="A12" s="1" t="s">
@@ -2066,21 +2055,11 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="O12" s="2">
-        <v>6</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q12" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M12" s="8"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="12"/>
+      <c r="Q12" s="16"/>
     </row>
     <row r="13" spans="1:17">
       <c r="A13" s="1" t="s">
@@ -2089,21 +2068,11 @@
       <c r="B13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O13" s="2">
-        <v>6</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q13" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M13" s="8"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="12"/>
+      <c r="Q13" s="17"/>
     </row>
     <row r="14" spans="1:17">
       <c r="A14" s="1" t="s">
@@ -2112,21 +2081,11 @@
       <c r="B14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="O14" s="2">
-        <v>6</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q14" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M14" s="8"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="12"/>
+      <c r="Q14" s="16"/>
     </row>
     <row r="15" spans="1:17">
       <c r="A15" s="1" t="s">
@@ -2135,21 +2094,11 @@
       <c r="B15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="O15" s="2">
-        <v>8</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M15" s="8"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="8"/>
+      <c r="P15" s="12"/>
+      <c r="Q15" s="17"/>
     </row>
     <row r="16" spans="1:17">
       <c r="A16" s="1" t="s">
@@ -2158,21 +2107,11 @@
       <c r="B16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="O16" s="2">
-        <v>6</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q16" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M16" s="8"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="12"/>
+      <c r="Q16" s="16"/>
     </row>
     <row r="17" spans="1:17">
       <c r="A17" s="1" t="s">
@@ -2181,21 +2120,11 @@
       <c r="B17" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="M17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="O17" s="2">
-        <v>5</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q17" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M17" s="8"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="12"/>
+      <c r="Q17" s="17"/>
     </row>
     <row r="18" spans="1:17">
       <c r="A18" s="1" t="s">
@@ -2204,21 +2133,11 @@
       <c r="B18" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="M18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="O18" s="2">
-        <v>5</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q18" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M18" s="8"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="16"/>
     </row>
     <row r="19" spans="1:17">
       <c r="A19" s="1" t="s">
@@ -2227,21 +2146,11 @@
       <c r="B19" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="M19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="O19" s="2">
-        <v>5</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M19" s="8"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="17"/>
     </row>
     <row r="20" spans="1:17">
       <c r="A20" s="1" t="s">
@@ -2250,21 +2159,11 @@
       <c r="B20" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M20" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="O20" s="2">
-        <v>5</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q20" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M20" s="8"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="16"/>
     </row>
     <row r="21" spans="1:17">
       <c r="A21" s="1" t="s">
@@ -2273,21 +2172,11 @@
       <c r="B21" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="O21" s="2">
-        <v>8</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M21" s="8"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="17"/>
     </row>
     <row r="22" spans="1:17">
       <c r="A22" s="1" t="s">
@@ -2296,21 +2185,11 @@
       <c r="B22" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="O22" s="2">
-        <v>7</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q22" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M22" s="8"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="16"/>
     </row>
     <row r="23" spans="1:17">
       <c r="A23" s="1" t="s">
@@ -2319,21 +2198,11 @@
       <c r="B23" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="O23" s="2">
-        <v>7</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M23" s="8"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="17"/>
     </row>
     <row r="24" spans="1:17">
       <c r="A24" s="1" t="s">
@@ -2342,21 +2211,11 @@
       <c r="B24" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M24" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="O24" s="2">
-        <v>7</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q24" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M24" s="8"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="16"/>
     </row>
     <row r="25" spans="1:17">
       <c r="A25" s="1" t="s">
@@ -2365,21 +2224,11 @@
       <c r="B25" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M25" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="O25" s="2">
-        <v>7</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M25" s="8"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="8"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="17"/>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" s="1" t="s">
@@ -2388,21 +2237,11 @@
       <c r="B26" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M26" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O26" s="2">
-        <v>7</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q26" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M26" s="8"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="8"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="16"/>
     </row>
     <row r="27" spans="1:17">
       <c r="A27" s="1" t="s">
@@ -2411,21 +2250,11 @@
       <c r="B27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M27" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="O27" s="2">
-        <v>7</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q27" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M27" s="8"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="8"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="17"/>
     </row>
     <row r="28" spans="1:17">
       <c r="A28" s="1" t="s">
@@ -2434,21 +2263,11 @@
       <c r="B28" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M28" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O28" s="2">
-        <v>8</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q28" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M28" s="8"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="8"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="16"/>
     </row>
     <row r="29" spans="1:17">
       <c r="A29" s="1" t="s">
@@ -2457,21 +2276,11 @@
       <c r="B29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M29" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="O29" s="2">
-        <v>5</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q29" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M29" s="8"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="8"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="17"/>
     </row>
     <row r="30" spans="1:17">
       <c r="A30" s="1" t="s">
@@ -2480,21 +2289,11 @@
       <c r="B30" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="M30" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O30" s="2">
-        <v>5</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q30" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M30" s="8"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="8"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="16"/>
     </row>
     <row r="31" spans="1:17">
       <c r="A31" s="1" t="s">
@@ -2503,21 +2302,11 @@
       <c r="B31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="M31" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O31" s="2">
-        <v>5</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q31" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M31" s="8"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="8"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="17"/>
     </row>
     <row r="32" spans="1:17">
       <c r="A32" s="1" t="s">
@@ -2526,21 +2315,11 @@
       <c r="B32" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="M32" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="O32" s="2">
-        <v>5</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q32" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M32" s="8"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="8"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="16"/>
     </row>
     <row r="33" spans="1:17">
       <c r="A33" s="1" t="s">
@@ -2549,21 +2328,11 @@
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M33" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="O33" s="2">
-        <v>5</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q33" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M33" s="8"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="8"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="17"/>
     </row>
     <row r="34" spans="1:17">
       <c r="A34" s="1" t="s">
@@ -2572,21 +2341,11 @@
       <c r="B34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M34" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="O34" s="2">
-        <v>5</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q34" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M34" s="8"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="8"/>
+      <c r="P34" s="12"/>
+      <c r="Q34" s="16"/>
     </row>
     <row r="35" spans="1:17">
       <c r="A35" s="1" t="s">
@@ -2595,21 +2354,11 @@
       <c r="B35" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M35" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="O35" s="2">
-        <v>5</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q35" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M35" s="8"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="8"/>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="17"/>
     </row>
     <row r="36" spans="1:17">
       <c r="A36" s="1" t="s">
@@ -2618,21 +2367,11 @@
       <c r="B36" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M36" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="O36" s="2">
-        <v>5</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q36" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M36" s="8"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="8"/>
+      <c r="P36" s="12"/>
+      <c r="Q36" s="16"/>
     </row>
     <row r="37" spans="1:17">
       <c r="A37" s="1" t="s">
@@ -2641,21 +2380,11 @@
       <c r="B37" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="M37" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="O37" s="2">
-        <v>5</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q37" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M37" s="8"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="8"/>
+      <c r="P37" s="12"/>
+      <c r="Q37" s="17"/>
     </row>
     <row r="38" spans="1:17">
       <c r="A38" s="1" t="s">
@@ -2664,21 +2393,11 @@
       <c r="B38" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O38" s="2">
-        <v>5</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q38" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M38" s="8"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="8"/>
+      <c r="P38" s="12"/>
+      <c r="Q38" s="16"/>
     </row>
     <row r="39" spans="1:17">
       <c r="A39" s="1" t="s">
@@ -2687,21 +2406,11 @@
       <c r="B39" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="M39" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="O39" s="2">
-        <v>5</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q39" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M39" s="8"/>
+      <c r="N39" s="12"/>
+      <c r="O39" s="8"/>
+      <c r="P39" s="12"/>
+      <c r="Q39" s="17"/>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" s="1" t="s">
@@ -2710,21 +2419,11 @@
       <c r="B40" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M40" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="O40" s="2">
-        <v>5</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q40" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M40" s="8"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="8"/>
+      <c r="P40" s="12"/>
+      <c r="Q40" s="16"/>
     </row>
     <row r="41" spans="1:17">
       <c r="A41" s="1" t="s">
@@ -2733,21 +2432,11 @@
       <c r="B41" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M41" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="O41" s="2">
-        <v>5</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q41" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M41" s="8"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="8"/>
+      <c r="P41" s="12"/>
+      <c r="Q41" s="17"/>
     </row>
     <row r="42" spans="1:17">
       <c r="A42" s="1" t="s">
@@ -2756,21 +2445,11 @@
       <c r="B42" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M42" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="O42" s="2">
-        <v>5</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q42" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M42" s="8"/>
+      <c r="N42" s="12"/>
+      <c r="O42" s="8"/>
+      <c r="P42" s="12"/>
+      <c r="Q42" s="16"/>
     </row>
     <row r="43" spans="1:17">
       <c r="A43" s="1" t="s">
@@ -2779,21 +2458,11 @@
       <c r="B43" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="M43" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="O43" s="2">
-        <v>5</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q43" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M43" s="8"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="8"/>
+      <c r="P43" s="12"/>
+      <c r="Q43" s="17"/>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" s="1" t="s">
@@ -2802,21 +2471,11 @@
       <c r="B44" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M44" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="O44" s="2">
-        <v>5</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q44" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M44" s="8"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="8"/>
+      <c r="P44" s="12"/>
+      <c r="Q44" s="16"/>
     </row>
     <row r="45" spans="1:17">
       <c r="A45" s="1" t="s">
@@ -2825,21 +2484,11 @@
       <c r="B45" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M45" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="O45" s="2">
-        <v>5</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q45" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="M45" s="8"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="8"/>
+      <c r="P45" s="12"/>
+      <c r="Q45" s="17"/>
     </row>
     <row r="46" spans="1:17">
       <c r="A46" s="1" t="s">
@@ -2848,21 +2497,11 @@
       <c r="B46" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M46" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O46" s="2">
-        <v>5</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q46" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M46" s="8"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="8"/>
+      <c r="P46" s="12"/>
+      <c r="Q46" s="16"/>
     </row>
     <row r="47" spans="1:17">
       <c r="A47" s="1" t="s">
@@ -2871,21 +2510,11 @@
       <c r="B47" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M47" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="N47" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="O47" s="15">
-        <v>5</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q47" s="5" t="s">
-        <v>65</v>
-      </c>
+      <c r="M47" s="8"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="8"/>
+      <c r="P47" s="12"/>
+      <c r="Q47" s="16"/>
     </row>
     <row r="48" spans="1:17">
       <c r="A48" s="1" t="s">
@@ -2934,30 +2563,14 @@
       <c r="B53" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M53" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="R53" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="S53" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="T53" s="1" t="s">
-        <v>137</v>
-      </c>
+      <c r="M53" s="12"/>
+      <c r="N53" s="12"/>
+      <c r="O53" s="12"/>
+      <c r="P53" s="12"/>
+      <c r="Q53" s="12"/>
+      <c r="R53" s="12"/>
+      <c r="S53" s="12"/>
+      <c r="T53" s="12"/>
     </row>
     <row r="54" spans="1:20">
       <c r="A54" s="2" t="s">
@@ -2966,30 +2579,14 @@
       <c r="B54" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="M54" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="N54" s="1" t="s">
-        <v>300</v>
-      </c>
-      <c r="O54" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P54" s="1">
-        <v>30</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R54" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S54" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T54" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
+      <c r="P54" s="12"/>
+      <c r="Q54" s="12"/>
+      <c r="R54" s="12"/>
+      <c r="S54" s="12"/>
+      <c r="T54" s="12"/>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" s="2" t="s">
@@ -2998,30 +2595,14 @@
       <c r="B55" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M55" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="N55" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="O55" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P55" s="1">
-        <v>38</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R55" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S55" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T55" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M55" s="12"/>
+      <c r="N55" s="12"/>
+      <c r="O55" s="12"/>
+      <c r="P55" s="12"/>
+      <c r="Q55" s="12"/>
+      <c r="R55" s="12"/>
+      <c r="S55" s="12"/>
+      <c r="T55" s="12"/>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" s="2" t="s">
@@ -3030,30 +2611,14 @@
       <c r="B56" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="M56" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>301</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P56" s="1">
-        <v>42</v>
-      </c>
-      <c r="Q56" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R56" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S56" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T56" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M56" s="12"/>
+      <c r="N56" s="12"/>
+      <c r="O56" s="12"/>
+      <c r="P56" s="12"/>
+      <c r="Q56" s="12"/>
+      <c r="R56" s="12"/>
+      <c r="S56" s="12"/>
+      <c r="T56" s="12"/>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" s="1" t="s">
@@ -3062,30 +2627,14 @@
       <c r="B57" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M57" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="N57" s="1" t="s">
-        <v>324</v>
-      </c>
-      <c r="O57" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P57" s="1">
-        <v>38</v>
-      </c>
-      <c r="Q57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R57" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="M57" s="12"/>
+      <c r="N57" s="12"/>
+      <c r="O57" s="12"/>
+      <c r="P57" s="12"/>
+      <c r="Q57" s="12"/>
+      <c r="R57" s="12"/>
+      <c r="S57" s="12"/>
+      <c r="T57" s="12"/>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" s="1" t="s">
@@ -3094,30 +2643,14 @@
       <c r="B58" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M58" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="N58" s="1" t="s">
-        <v>325</v>
-      </c>
-      <c r="O58" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P58" s="1">
-        <v>41</v>
-      </c>
-      <c r="Q58" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R58" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S58" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T58" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="M58" s="12"/>
+      <c r="N58" s="12"/>
+      <c r="O58" s="12"/>
+      <c r="P58" s="12"/>
+      <c r="Q58" s="12"/>
+      <c r="R58" s="12"/>
+      <c r="S58" s="12"/>
+      <c r="T58" s="12"/>
     </row>
     <row r="59" spans="1:20">
       <c r="A59" s="1" t="s">
@@ -3126,30 +2659,14 @@
       <c r="B59" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M59" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="N59" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P59" s="1">
-        <v>44</v>
-      </c>
-      <c r="Q59" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R59" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S59" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T59" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M59" s="12"/>
+      <c r="N59" s="12"/>
+      <c r="O59" s="12"/>
+      <c r="P59" s="12"/>
+      <c r="Q59" s="12"/>
+      <c r="R59" s="12"/>
+      <c r="S59" s="12"/>
+      <c r="T59" s="12"/>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" s="1" t="s">
@@ -3158,30 +2675,14 @@
       <c r="B60" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M60" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="N60" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="O60" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P60" s="1">
-        <v>44</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R60" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S60" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T60" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M60" s="12"/>
+      <c r="N60" s="12"/>
+      <c r="O60" s="12"/>
+      <c r="P60" s="12"/>
+      <c r="Q60" s="12"/>
+      <c r="R60" s="12"/>
+      <c r="S60" s="12"/>
+      <c r="T60" s="12"/>
     </row>
     <row r="61" spans="1:20">
       <c r="A61" s="1" t="s">
@@ -3190,30 +2691,14 @@
       <c r="B61" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M61" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>303</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P61" s="1">
-        <v>40</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R61" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T61" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
+      <c r="P61" s="12"/>
+      <c r="Q61" s="12"/>
+      <c r="R61" s="12"/>
+      <c r="S61" s="12"/>
+      <c r="T61" s="12"/>
     </row>
     <row r="62" spans="1:20">
       <c r="A62" s="1" t="s">
@@ -3222,30 +2707,14 @@
       <c r="B62" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="M62" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P62" s="1">
-        <v>42</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R62" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S62" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T62" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
+      <c r="P62" s="12"/>
+      <c r="Q62" s="12"/>
+      <c r="R62" s="12"/>
+      <c r="S62" s="12"/>
+      <c r="T62" s="12"/>
     </row>
     <row r="63" spans="1:20">
       <c r="A63" s="1" t="s">
@@ -3254,30 +2723,14 @@
       <c r="B63" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M63" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>327</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P63" s="1">
-        <v>43</v>
-      </c>
-      <c r="Q63" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R63" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S63" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T63" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="M63" s="12"/>
+      <c r="N63" s="12"/>
+      <c r="O63" s="12"/>
+      <c r="P63" s="12"/>
+      <c r="Q63" s="12"/>
+      <c r="R63" s="12"/>
+      <c r="S63" s="12"/>
+      <c r="T63" s="12"/>
     </row>
     <row r="64" spans="1:20">
       <c r="A64" s="1" t="s">
@@ -3286,30 +2739,14 @@
       <c r="B64" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M64" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="N64" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="O64" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P64" s="1">
-        <v>44</v>
-      </c>
-      <c r="Q64" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R64" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S64" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T64" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="M64" s="12"/>
+      <c r="N64" s="12"/>
+      <c r="O64" s="12"/>
+      <c r="P64" s="12"/>
+      <c r="Q64" s="12"/>
+      <c r="R64" s="12"/>
+      <c r="S64" s="12"/>
+      <c r="T64" s="12"/>
     </row>
     <row r="65" spans="1:20">
       <c r="A65" s="1" t="s">
@@ -3318,30 +2755,14 @@
       <c r="B65" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M65" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="O65" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P65" s="1">
-        <v>38</v>
-      </c>
-      <c r="Q65" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R65" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S65" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T65" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M65" s="12"/>
+      <c r="N65" s="12"/>
+      <c r="O65" s="12"/>
+      <c r="P65" s="12"/>
+      <c r="Q65" s="12"/>
+      <c r="R65" s="12"/>
+      <c r="S65" s="12"/>
+      <c r="T65" s="12"/>
     </row>
     <row r="66" spans="1:20">
       <c r="A66" s="1" t="s">
@@ -3350,30 +2771,14 @@
       <c r="B66" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M66" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N66" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="O66" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P66" s="1">
-        <v>40</v>
-      </c>
-      <c r="Q66" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R66" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S66" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T66" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+      <c r="O66" s="12"/>
+      <c r="P66" s="12"/>
+      <c r="Q66" s="12"/>
+      <c r="R66" s="12"/>
+      <c r="S66" s="12"/>
+      <c r="T66" s="12"/>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" s="1" t="s">
@@ -3382,30 +2787,14 @@
       <c r="B67" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="M67" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="N67" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="O67" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P67" s="1">
-        <v>40</v>
-      </c>
-      <c r="Q67" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R67" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S67" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T67" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M67" s="12"/>
+      <c r="N67" s="12"/>
+      <c r="O67" s="12"/>
+      <c r="P67" s="12"/>
+      <c r="Q67" s="12"/>
+      <c r="R67" s="12"/>
+      <c r="S67" s="12"/>
+      <c r="T67" s="12"/>
     </row>
     <row r="68" spans="1:20">
       <c r="A68" s="1" t="s">
@@ -3414,30 +2803,14 @@
       <c r="B68" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M68" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="N68" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="O68" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P68" s="1">
-        <v>35</v>
-      </c>
-      <c r="Q68" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R68" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S68" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T68" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M68" s="12"/>
+      <c r="N68" s="12"/>
+      <c r="O68" s="12"/>
+      <c r="P68" s="12"/>
+      <c r="Q68" s="12"/>
+      <c r="R68" s="12"/>
+      <c r="S68" s="12"/>
+      <c r="T68" s="12"/>
     </row>
     <row r="69" spans="1:20">
       <c r="A69" s="1" t="s">
@@ -3446,30 +2819,14 @@
       <c r="B69" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M69" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="O69" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P69" s="1">
-        <v>38</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R69" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S69" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T69" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M69" s="12"/>
+      <c r="N69" s="12"/>
+      <c r="O69" s="12"/>
+      <c r="P69" s="12"/>
+      <c r="Q69" s="12"/>
+      <c r="R69" s="12"/>
+      <c r="S69" s="12"/>
+      <c r="T69" s="12"/>
     </row>
     <row r="70" spans="1:20">
       <c r="A70" s="1" t="s">
@@ -3478,30 +2835,14 @@
       <c r="B70" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M70" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="N70" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="O70" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P70" s="1">
-        <v>42</v>
-      </c>
-      <c r="Q70" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R70" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S70" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T70" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M70" s="12"/>
+      <c r="N70" s="12"/>
+      <c r="O70" s="12"/>
+      <c r="P70" s="12"/>
+      <c r="Q70" s="12"/>
+      <c r="R70" s="12"/>
+      <c r="S70" s="12"/>
+      <c r="T70" s="12"/>
     </row>
     <row r="71" spans="1:20">
       <c r="A71" s="1" t="s">
@@ -3510,30 +2851,14 @@
       <c r="B71" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M71" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="N71" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="O71" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P71" s="1">
-        <v>40</v>
-      </c>
-      <c r="Q71" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R71" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S71" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T71" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M71" s="12"/>
+      <c r="N71" s="12"/>
+      <c r="O71" s="12"/>
+      <c r="P71" s="12"/>
+      <c r="Q71" s="12"/>
+      <c r="R71" s="12"/>
+      <c r="S71" s="12"/>
+      <c r="T71" s="12"/>
     </row>
     <row r="72" spans="1:20">
       <c r="A72" s="1" t="s">
@@ -3542,30 +2867,14 @@
       <c r="B72" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M72" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="N72" s="1" t="s">
-        <v>319</v>
-      </c>
-      <c r="O72" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P72" s="1">
-        <v>44</v>
-      </c>
-      <c r="Q72" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R72" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S72" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T72" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M72" s="12"/>
+      <c r="N72" s="12"/>
+      <c r="O72" s="12"/>
+      <c r="P72" s="12"/>
+      <c r="Q72" s="12"/>
+      <c r="R72" s="12"/>
+      <c r="S72" s="12"/>
+      <c r="T72" s="12"/>
     </row>
     <row r="73" spans="1:20">
       <c r="A73" s="1" t="s">
@@ -3574,30 +2883,14 @@
       <c r="B73" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M73" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="N73" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="O73" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P73" s="1">
-        <v>41</v>
-      </c>
-      <c r="Q73" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R73" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S73" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T73" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M73" s="12"/>
+      <c r="N73" s="12"/>
+      <c r="O73" s="12"/>
+      <c r="P73" s="12"/>
+      <c r="Q73" s="12"/>
+      <c r="R73" s="12"/>
+      <c r="S73" s="12"/>
+      <c r="T73" s="12"/>
     </row>
     <row r="74" spans="1:20">
       <c r="A74" s="1" t="s">
@@ -3606,30 +2899,14 @@
       <c r="B74" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M74" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="N74" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="O74" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P74" s="1">
-        <v>44</v>
-      </c>
-      <c r="Q74" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R74" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S74" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T74" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M74" s="12"/>
+      <c r="N74" s="12"/>
+      <c r="O74" s="12"/>
+      <c r="P74" s="12"/>
+      <c r="Q74" s="12"/>
+      <c r="R74" s="12"/>
+      <c r="S74" s="12"/>
+      <c r="T74" s="12"/>
     </row>
     <row r="75" spans="1:20">
       <c r="A75" s="1" t="s">
@@ -3638,30 +2915,14 @@
       <c r="B75" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M75" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="N75" s="1" t="s">
-        <v>320</v>
-      </c>
-      <c r="O75" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P75" s="1">
-        <v>42</v>
-      </c>
-      <c r="Q75" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R75" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S75" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T75" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M75" s="12"/>
+      <c r="N75" s="12"/>
+      <c r="O75" s="12"/>
+      <c r="P75" s="12"/>
+      <c r="Q75" s="12"/>
+      <c r="R75" s="12"/>
+      <c r="S75" s="12"/>
+      <c r="T75" s="12"/>
     </row>
     <row r="76" spans="1:20">
       <c r="A76" s="1" t="s">
@@ -3670,30 +2931,14 @@
       <c r="B76" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M76" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="N76" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="O76" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P76" s="1">
-        <v>44</v>
-      </c>
-      <c r="Q76" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R76" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S76" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T76" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M76" s="12"/>
+      <c r="N76" s="12"/>
+      <c r="O76" s="12"/>
+      <c r="P76" s="12"/>
+      <c r="Q76" s="12"/>
+      <c r="R76" s="12"/>
+      <c r="S76" s="12"/>
+      <c r="T76" s="12"/>
     </row>
     <row r="77" spans="1:20">
       <c r="A77" s="1" t="s">
@@ -3702,30 +2947,14 @@
       <c r="B77" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M77" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="N77" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="O77" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P77" s="1">
-        <v>40</v>
-      </c>
-      <c r="Q77" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R77" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S77" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T77" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M77" s="12"/>
+      <c r="N77" s="12"/>
+      <c r="O77" s="12"/>
+      <c r="P77" s="12"/>
+      <c r="Q77" s="12"/>
+      <c r="R77" s="12"/>
+      <c r="S77" s="12"/>
+      <c r="T77" s="12"/>
     </row>
     <row r="78" spans="1:20">
       <c r="A78" s="1" t="s">
@@ -3734,30 +2963,14 @@
       <c r="B78" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M78" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="N78" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="O78" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P78" s="1">
-        <v>42</v>
-      </c>
-      <c r="Q78" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R78" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S78" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T78" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M78" s="12"/>
+      <c r="N78" s="12"/>
+      <c r="O78" s="12"/>
+      <c r="P78" s="12"/>
+      <c r="Q78" s="12"/>
+      <c r="R78" s="12"/>
+      <c r="S78" s="12"/>
+      <c r="T78" s="12"/>
     </row>
     <row r="79" spans="1:20">
       <c r="A79" s="1" t="s">
@@ -3766,30 +2979,14 @@
       <c r="B79" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M79" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="N79" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="O79" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P79" s="1">
-        <v>16</v>
-      </c>
-      <c r="Q79" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R79" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S79" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="T79" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="M79" s="12"/>
+      <c r="N79" s="12"/>
+      <c r="O79" s="12"/>
+      <c r="P79" s="12"/>
+      <c r="Q79" s="12"/>
+      <c r="R79" s="12"/>
+      <c r="S79" s="18"/>
+      <c r="T79" s="12"/>
     </row>
     <row r="80" spans="1:20">
       <c r="A80" s="1" t="s">
@@ -3798,30 +2995,14 @@
       <c r="B80" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M80" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="N80" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="O80" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P80" s="1">
-        <v>44</v>
-      </c>
-      <c r="Q80" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R80" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S80" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T80" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M80" s="12"/>
+      <c r="N80" s="12"/>
+      <c r="O80" s="12"/>
+      <c r="P80" s="12"/>
+      <c r="Q80" s="12"/>
+      <c r="R80" s="12"/>
+      <c r="S80" s="12"/>
+      <c r="T80" s="12"/>
     </row>
     <row r="81" spans="1:20">
       <c r="A81" s="1" t="s">
@@ -3830,30 +3011,14 @@
       <c r="B81" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M81" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="N81" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="O81" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P81" s="1">
-        <v>38</v>
-      </c>
-      <c r="Q81" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R81" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S81" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T81" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M81" s="12"/>
+      <c r="N81" s="12"/>
+      <c r="O81" s="12"/>
+      <c r="P81" s="12"/>
+      <c r="Q81" s="12"/>
+      <c r="R81" s="12"/>
+      <c r="S81" s="12"/>
+      <c r="T81" s="12"/>
     </row>
     <row r="82" spans="1:20">
       <c r="A82" s="1" t="s">
@@ -3862,30 +3027,14 @@
       <c r="B82" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M82" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="N82" s="1" t="s">
-        <v>329</v>
-      </c>
-      <c r="O82" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P82" s="1">
-        <v>42</v>
-      </c>
-      <c r="Q82" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R82" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S82" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T82" s="1" t="s">
-        <v>129</v>
-      </c>
+      <c r="M82" s="12"/>
+      <c r="N82" s="12"/>
+      <c r="O82" s="12"/>
+      <c r="P82" s="12"/>
+      <c r="Q82" s="12"/>
+      <c r="R82" s="12"/>
+      <c r="S82" s="12"/>
+      <c r="T82" s="12"/>
     </row>
     <row r="83" spans="1:20">
       <c r="A83" s="1" t="s">
@@ -3894,30 +3043,14 @@
       <c r="B83" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M83" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="N83" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P83" s="1">
-        <v>38</v>
-      </c>
-      <c r="Q83" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R83" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S83" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T83" s="1" t="s">
-        <v>128</v>
-      </c>
+      <c r="M83" s="12"/>
+      <c r="N83" s="12"/>
+      <c r="O83" s="12"/>
+      <c r="P83" s="12"/>
+      <c r="Q83" s="12"/>
+      <c r="R83" s="12"/>
+      <c r="S83" s="12"/>
+      <c r="T83" s="12"/>
     </row>
     <row r="84" spans="1:20">
       <c r="A84" s="1" t="s">
@@ -3926,30 +3059,14 @@
       <c r="B84" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M84" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="N84" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="O84" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P84" s="1">
-        <v>30</v>
-      </c>
-      <c r="Q84" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R84" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S84" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T84" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M84" s="12"/>
+      <c r="N84" s="12"/>
+      <c r="O84" s="12"/>
+      <c r="P84" s="12"/>
+      <c r="Q84" s="12"/>
+      <c r="R84" s="12"/>
+      <c r="S84" s="12"/>
+      <c r="T84" s="12"/>
     </row>
     <row r="85" spans="1:20">
       <c r="A85" s="1" t="s">
@@ -3958,30 +3075,14 @@
       <c r="B85" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="M85" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="N85" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="O85" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P85" s="1">
-        <v>30</v>
-      </c>
-      <c r="Q85" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R85" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S85" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T85" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M85" s="12"/>
+      <c r="N85" s="12"/>
+      <c r="O85" s="12"/>
+      <c r="P85" s="12"/>
+      <c r="Q85" s="12"/>
+      <c r="R85" s="12"/>
+      <c r="S85" s="12"/>
+      <c r="T85" s="12"/>
     </row>
     <row r="86" spans="1:20">
       <c r="A86" s="1" t="s">
@@ -3990,30 +3091,14 @@
       <c r="B86" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="M86" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="N86" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="O86" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P86" s="1">
-        <v>45</v>
-      </c>
-      <c r="Q86" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R86" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S86" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="T86" s="1" t="s">
-        <v>130</v>
-      </c>
+      <c r="M86" s="12"/>
+      <c r="N86" s="12"/>
+      <c r="O86" s="12"/>
+      <c r="P86" s="12"/>
+      <c r="Q86" s="12"/>
+      <c r="R86" s="12"/>
+      <c r="S86" s="12"/>
+      <c r="T86" s="12"/>
     </row>
     <row r="87" spans="1:20">
       <c r="A87" s="1" t="s">
@@ -4022,30 +3107,14 @@
       <c r="B87" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M87" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="N87" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="O87" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P87" s="1">
-        <v>22</v>
-      </c>
-      <c r="Q87" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R87" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S87" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="T87" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="M87" s="12"/>
+      <c r="N87" s="12"/>
+      <c r="O87" s="12"/>
+      <c r="P87" s="12"/>
+      <c r="Q87" s="12"/>
+      <c r="R87" s="12"/>
+      <c r="S87" s="12"/>
+      <c r="T87" s="12"/>
     </row>
     <row r="88" spans="1:20">
       <c r="A88" s="1" t="s">
@@ -4054,30 +3123,14 @@
       <c r="B88" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M88" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="N88" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="O88" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P88" s="1">
-        <v>32</v>
-      </c>
-      <c r="Q88" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R88" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S88" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="T88" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="M88" s="12"/>
+      <c r="N88" s="12"/>
+      <c r="O88" s="12"/>
+      <c r="P88" s="12"/>
+      <c r="Q88" s="12"/>
+      <c r="R88" s="12"/>
+      <c r="S88" s="12"/>
+      <c r="T88" s="12"/>
     </row>
     <row r="89" spans="1:20">
       <c r="A89" s="1" t="s">
@@ -4086,30 +3139,14 @@
       <c r="B89" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M89" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="N89" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="O89" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P89" s="1">
-        <v>35</v>
-      </c>
-      <c r="Q89" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R89" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S89" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="T89" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="M89" s="12"/>
+      <c r="N89" s="12"/>
+      <c r="O89" s="12"/>
+      <c r="P89" s="12"/>
+      <c r="Q89" s="12"/>
+      <c r="R89" s="12"/>
+      <c r="S89" s="12"/>
+      <c r="T89" s="12"/>
     </row>
     <row r="90" spans="1:20">
       <c r="A90" s="1" t="s">
@@ -4118,30 +3155,14 @@
       <c r="B90" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="M90" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="N90" s="1" t="s">
-        <v>330</v>
-      </c>
-      <c r="O90" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P90" s="1">
-        <v>32</v>
-      </c>
-      <c r="Q90" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R90" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S90" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="T90" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="M90" s="12"/>
+      <c r="N90" s="12"/>
+      <c r="O90" s="12"/>
+      <c r="P90" s="12"/>
+      <c r="Q90" s="12"/>
+      <c r="R90" s="12"/>
+      <c r="S90" s="12"/>
+      <c r="T90" s="12"/>
     </row>
     <row r="91" spans="1:20">
       <c r="A91" s="1" t="s">
@@ -4150,30 +3171,14 @@
       <c r="B91" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="M91" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="N91" s="1" t="s">
-        <v>331</v>
-      </c>
-      <c r="O91" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P91" s="1">
-        <v>32</v>
-      </c>
-      <c r="Q91" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R91" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S91" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="T91" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="M91" s="12"/>
+      <c r="N91" s="12"/>
+      <c r="O91" s="12"/>
+      <c r="P91" s="12"/>
+      <c r="Q91" s="12"/>
+      <c r="R91" s="12"/>
+      <c r="S91" s="12"/>
+      <c r="T91" s="12"/>
     </row>
     <row r="92" spans="1:20">
       <c r="A92" s="1" t="s">
@@ -4182,30 +3187,14 @@
       <c r="B92" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M92" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="N92" s="1" t="s">
-        <v>332</v>
-      </c>
-      <c r="O92" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P92" s="1">
-        <v>34</v>
-      </c>
-      <c r="Q92" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R92" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S92" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="T92" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="M92" s="12"/>
+      <c r="N92" s="12"/>
+      <c r="O92" s="12"/>
+      <c r="P92" s="12"/>
+      <c r="Q92" s="12"/>
+      <c r="R92" s="12"/>
+      <c r="S92" s="12"/>
+      <c r="T92" s="12"/>
     </row>
     <row r="93" spans="1:20">
       <c r="A93" s="1" t="s">
@@ -4214,30 +3203,14 @@
       <c r="B93" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="M93" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>333</v>
-      </c>
-      <c r="O93" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="P93" s="1">
-        <v>34</v>
-      </c>
-      <c r="Q93" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R93" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S93" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="T93" s="1" t="s">
-        <v>143</v>
-      </c>
+      <c r="M93" s="12"/>
+      <c r="N93" s="12"/>
+      <c r="O93" s="12"/>
+      <c r="P93" s="12"/>
+      <c r="Q93" s="12"/>
+      <c r="R93" s="12"/>
+      <c r="S93" s="12"/>
+      <c r="T93" s="12"/>
     </row>
     <row r="94" spans="1:20">
       <c r="A94" s="1" t="s">
@@ -4246,30 +3219,14 @@
       <c r="B94" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M94" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>334</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P94" s="1">
-        <v>16</v>
-      </c>
-      <c r="Q94" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R94" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S94" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="T94" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="M94" s="12"/>
+      <c r="N94" s="12"/>
+      <c r="O94" s="12"/>
+      <c r="P94" s="12"/>
+      <c r="Q94" s="12"/>
+      <c r="R94" s="12"/>
+      <c r="S94" s="18"/>
+      <c r="T94" s="8"/>
     </row>
     <row r="95" spans="1:20">
       <c r="A95" s="1" t="s">
@@ -4278,30 +3235,14 @@
       <c r="B95" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M95" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="N95" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="O95" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P95" s="1">
-        <v>9</v>
-      </c>
-      <c r="Q95" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R95" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S95" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T95" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M95" s="8"/>
+      <c r="N95" s="12"/>
+      <c r="O95" s="12"/>
+      <c r="P95" s="12"/>
+      <c r="Q95" s="12"/>
+      <c r="R95" s="12"/>
+      <c r="S95" s="8"/>
+      <c r="T95" s="8"/>
     </row>
     <row r="96" spans="1:20">
       <c r="A96" s="1" t="s">
@@ -4310,30 +3251,14 @@
       <c r="B96" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="M96" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="N96" s="1" t="s">
-        <v>367</v>
-      </c>
-      <c r="O96" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P96" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q96" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R96" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S96" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="T96" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="M96" s="8"/>
+      <c r="N96" s="12"/>
+      <c r="O96" s="12"/>
+      <c r="P96" s="12"/>
+      <c r="Q96" s="12"/>
+      <c r="R96" s="12"/>
+      <c r="S96" s="8"/>
+      <c r="T96" s="8"/>
     </row>
     <row r="97" spans="1:20">
       <c r="A97" s="1" t="s">
@@ -4342,30 +3267,14 @@
       <c r="B97" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M97" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="N97" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P97" s="1">
-        <v>7</v>
-      </c>
-      <c r="Q97" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R97" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S97" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T97" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="M97" s="8"/>
+      <c r="N97" s="12"/>
+      <c r="O97" s="12"/>
+      <c r="P97" s="12"/>
+      <c r="Q97" s="12"/>
+      <c r="R97" s="12"/>
+      <c r="S97" s="8"/>
+      <c r="T97" s="8"/>
     </row>
     <row r="98" spans="1:20">
       <c r="A98" s="1" t="s">
@@ -4374,30 +3283,14 @@
       <c r="B98" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M98" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="N98" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="O98" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P98" s="1">
-        <v>8</v>
-      </c>
-      <c r="Q98" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R98" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S98" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T98" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="M98" s="8"/>
+      <c r="N98" s="12"/>
+      <c r="O98" s="12"/>
+      <c r="P98" s="12"/>
+      <c r="Q98" s="12"/>
+      <c r="R98" s="12"/>
+      <c r="S98" s="8"/>
+      <c r="T98" s="8"/>
     </row>
     <row r="99" spans="1:20">
       <c r="A99" s="1" t="s">
@@ -4406,30 +3299,14 @@
       <c r="B99" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M99" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="N99" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="O99" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P99" s="1">
-        <v>7</v>
-      </c>
-      <c r="Q99" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R99" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S99" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T99" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="M99" s="8"/>
+      <c r="N99" s="12"/>
+      <c r="O99" s="12"/>
+      <c r="P99" s="12"/>
+      <c r="Q99" s="12"/>
+      <c r="R99" s="12"/>
+      <c r="S99" s="8"/>
+      <c r="T99" s="8"/>
     </row>
     <row r="100" spans="1:20">
       <c r="A100" s="1" t="s">
@@ -4438,30 +3315,14 @@
       <c r="B100" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M100" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="N100" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="O100" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P100" s="1">
-        <v>7</v>
-      </c>
-      <c r="Q100" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R100" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S100" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T100" s="2" t="s">
-        <v>132</v>
-      </c>
+      <c r="M100" s="8"/>
+      <c r="N100" s="12"/>
+      <c r="O100" s="12"/>
+      <c r="P100" s="12"/>
+      <c r="Q100" s="12"/>
+      <c r="R100" s="12"/>
+      <c r="S100" s="8"/>
+      <c r="T100" s="8"/>
     </row>
     <row r="101" spans="1:20">
       <c r="A101" s="1" t="s">
@@ -4470,30 +3331,14 @@
       <c r="B101" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M101" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="N101" s="1" t="s">
-        <v>336</v>
-      </c>
-      <c r="O101" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P101" s="1">
-        <v>13</v>
-      </c>
-      <c r="Q101" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R101" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S101" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="T101" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="M101" s="8"/>
+      <c r="N101" s="12"/>
+      <c r="O101" s="12"/>
+      <c r="P101" s="12"/>
+      <c r="Q101" s="12"/>
+      <c r="R101" s="12"/>
+      <c r="S101" s="9"/>
+      <c r="T101" s="8"/>
     </row>
     <row r="102" spans="1:20">
       <c r="A102" s="1" t="s">
@@ -4502,30 +3347,14 @@
       <c r="B102" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="M102" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="N102" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="O102" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="P102" s="13">
-        <v>15</v>
-      </c>
-      <c r="Q102" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="R102" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="S102" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="T102" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M102" s="8"/>
+      <c r="N102" s="12"/>
+      <c r="O102" s="12"/>
+      <c r="P102" s="12"/>
+      <c r="Q102" s="12"/>
+      <c r="R102" s="12"/>
+      <c r="S102" s="8"/>
+      <c r="T102" s="8"/>
     </row>
     <row r="103" spans="1:20">
       <c r="A103" s="1" t="s">
@@ -4534,30 +3363,14 @@
       <c r="B103" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M103" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="N103" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="O103" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P103" s="12">
-        <v>16</v>
-      </c>
-      <c r="Q103" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R103" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S103" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="T103" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M103" s="8"/>
+      <c r="N103" s="12"/>
+      <c r="O103" s="12"/>
+      <c r="P103" s="12"/>
+      <c r="Q103" s="12"/>
+      <c r="R103" s="12"/>
+      <c r="S103" s="9"/>
+      <c r="T103" s="8"/>
     </row>
     <row r="104" spans="1:20">
       <c r="A104" s="1" t="s">
@@ -4566,30 +3379,14 @@
       <c r="B104" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="M104" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="N104" s="12" t="s">
-        <v>339</v>
-      </c>
-      <c r="O104" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P104" s="12">
-        <v>15</v>
-      </c>
-      <c r="Q104" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R104" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S104" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="T104" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M104" s="8"/>
+      <c r="N104" s="12"/>
+      <c r="O104" s="12"/>
+      <c r="P104" s="12"/>
+      <c r="Q104" s="12"/>
+      <c r="R104" s="12"/>
+      <c r="S104" s="9"/>
+      <c r="T104" s="8"/>
     </row>
     <row r="105" spans="1:20">
       <c r="A105" s="1" t="s">
@@ -4598,30 +3395,14 @@
       <c r="B105" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M105" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="N105" s="12" t="s">
-        <v>340</v>
-      </c>
-      <c r="O105" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P105" s="12">
-        <v>18</v>
-      </c>
-      <c r="Q105" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R105" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S105" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="T105" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M105" s="8"/>
+      <c r="N105" s="12"/>
+      <c r="O105" s="12"/>
+      <c r="P105" s="12"/>
+      <c r="Q105" s="12"/>
+      <c r="R105" s="12"/>
+      <c r="S105" s="9"/>
+      <c r="T105" s="8"/>
     </row>
     <row r="106" spans="1:20">
       <c r="A106" s="1" t="s">
@@ -4630,30 +3411,14 @@
       <c r="B106" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M106" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="N106" s="12" t="s">
-        <v>341</v>
-      </c>
-      <c r="O106" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P106" s="12">
-        <v>18</v>
-      </c>
-      <c r="Q106" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R106" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S106" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T106" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M106" s="8"/>
+      <c r="N106" s="12"/>
+      <c r="O106" s="12"/>
+      <c r="P106" s="12"/>
+      <c r="Q106" s="12"/>
+      <c r="R106" s="12"/>
+      <c r="S106" s="8"/>
+      <c r="T106" s="8"/>
     </row>
     <row r="107" spans="1:20">
       <c r="A107" s="1" t="s">
@@ -4662,30 +3427,14 @@
       <c r="B107" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M107" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="N107" s="12" t="s">
-        <v>342</v>
-      </c>
-      <c r="O107" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P107" s="12">
-        <v>12</v>
-      </c>
-      <c r="Q107" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R107" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S107" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T107" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M107" s="8"/>
+      <c r="N107" s="12"/>
+      <c r="O107" s="12"/>
+      <c r="P107" s="12"/>
+      <c r="Q107" s="12"/>
+      <c r="R107" s="12"/>
+      <c r="S107" s="8"/>
+      <c r="T107" s="8"/>
     </row>
     <row r="108" spans="1:20">
       <c r="A108" s="1" t="s">
@@ -4694,30 +3443,14 @@
       <c r="B108" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="M108" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="N108" s="12" t="s">
-        <v>343</v>
-      </c>
-      <c r="O108" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P108" s="12">
-        <v>12</v>
-      </c>
-      <c r="Q108" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R108" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S108" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T108" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M108" s="8"/>
+      <c r="N108" s="12"/>
+      <c r="O108" s="12"/>
+      <c r="P108" s="12"/>
+      <c r="Q108" s="12"/>
+      <c r="R108" s="12"/>
+      <c r="S108" s="8"/>
+      <c r="T108" s="8"/>
     </row>
     <row r="109" spans="1:20">
       <c r="A109" s="1" t="s">
@@ -4726,30 +3459,14 @@
       <c r="B109" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="M109" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="N109" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="O109" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P109" s="12">
-        <v>10</v>
-      </c>
-      <c r="Q109" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R109" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S109" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T109" s="12" t="s">
-        <v>131</v>
-      </c>
+      <c r="M109" s="8"/>
+      <c r="N109" s="12"/>
+      <c r="O109" s="12"/>
+      <c r="P109" s="12"/>
+      <c r="Q109" s="12"/>
+      <c r="R109" s="12"/>
+      <c r="S109" s="8"/>
+      <c r="T109" s="12"/>
     </row>
     <row r="110" spans="1:20">
       <c r="A110" s="1" t="s">
@@ -4758,30 +3475,14 @@
       <c r="B110" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M110" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="N110" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="O110" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P110" s="12">
-        <v>12</v>
-      </c>
-      <c r="Q110" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R110" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S110" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T110" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M110" s="8"/>
+      <c r="N110" s="12"/>
+      <c r="O110" s="12"/>
+      <c r="P110" s="12"/>
+      <c r="Q110" s="12"/>
+      <c r="R110" s="12"/>
+      <c r="S110" s="8"/>
+      <c r="T110" s="8"/>
     </row>
     <row r="111" spans="1:20">
       <c r="A111" s="1" t="s">
@@ -4790,30 +3491,14 @@
       <c r="B111" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M111" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="N111" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="O111" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P111" s="12">
-        <v>7</v>
-      </c>
-      <c r="Q111" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R111" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S111" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T111" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M111" s="8"/>
+      <c r="N111" s="12"/>
+      <c r="O111" s="12"/>
+      <c r="P111" s="12"/>
+      <c r="Q111" s="12"/>
+      <c r="R111" s="12"/>
+      <c r="S111" s="8"/>
+      <c r="T111" s="8"/>
     </row>
     <row r="112" spans="1:20">
       <c r="A112" s="1" t="s">
@@ -4822,30 +3507,14 @@
       <c r="B112" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M112" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="N112" s="12" t="s">
-        <v>347</v>
-      </c>
-      <c r="O112" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P112" s="12">
-        <v>10</v>
-      </c>
-      <c r="Q112" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R112" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S112" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T112" s="2" t="s">
-        <v>131</v>
-      </c>
+      <c r="M112" s="8"/>
+      <c r="N112" s="12"/>
+      <c r="O112" s="12"/>
+      <c r="P112" s="12"/>
+      <c r="Q112" s="12"/>
+      <c r="R112" s="12"/>
+      <c r="S112" s="8"/>
+      <c r="T112" s="8"/>
     </row>
     <row r="113" spans="1:20">
       <c r="A113" s="1" t="s">
@@ -4854,30 +3523,14 @@
       <c r="B113" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M113" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="N113" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="O113" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P113" s="12">
-        <v>12</v>
-      </c>
-      <c r="Q113" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R113" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S113" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="T113" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="M113" s="8"/>
+      <c r="N113" s="12"/>
+      <c r="O113" s="12"/>
+      <c r="P113" s="12"/>
+      <c r="Q113" s="12"/>
+      <c r="R113" s="12"/>
+      <c r="S113" s="8"/>
+      <c r="T113" s="8"/>
     </row>
     <row r="114" spans="1:20">
       <c r="A114" s="1" t="s">
@@ -4886,30 +3539,14 @@
       <c r="B114" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="M114" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="N114" s="1" t="s">
-        <v>349</v>
-      </c>
-      <c r="O114" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P114" s="12">
-        <v>10</v>
-      </c>
-      <c r="Q114" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R114" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S114" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T114" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="M114" s="8"/>
+      <c r="N114" s="12"/>
+      <c r="O114" s="12"/>
+      <c r="P114" s="12"/>
+      <c r="Q114" s="12"/>
+      <c r="R114" s="12"/>
+      <c r="S114" s="8"/>
+      <c r="T114" s="8"/>
     </row>
     <row r="115" spans="1:20">
       <c r="A115" s="1" t="s">
@@ -4918,30 +3555,14 @@
       <c r="B115" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="M115" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="N115" s="12" t="s">
-        <v>363</v>
-      </c>
-      <c r="O115" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P115" s="12">
-        <v>10</v>
-      </c>
-      <c r="Q115" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R115" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S115" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T115" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="M115" s="8"/>
+      <c r="N115" s="12"/>
+      <c r="O115" s="12"/>
+      <c r="P115" s="12"/>
+      <c r="Q115" s="12"/>
+      <c r="R115" s="12"/>
+      <c r="S115" s="8"/>
+      <c r="T115" s="8"/>
     </row>
     <row r="116" spans="1:20">
       <c r="A116" s="1" t="s">
@@ -4950,30 +3571,14 @@
       <c r="B116" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="M116" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="N116" s="12" t="s">
-        <v>351</v>
-      </c>
-      <c r="O116" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P116" s="12">
-        <v>10</v>
-      </c>
-      <c r="Q116" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R116" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S116" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T116" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="M116" s="8"/>
+      <c r="N116" s="12"/>
+      <c r="O116" s="12"/>
+      <c r="P116" s="12"/>
+      <c r="Q116" s="12"/>
+      <c r="R116" s="12"/>
+      <c r="S116" s="8"/>
+      <c r="T116" s="8"/>
     </row>
     <row r="117" spans="1:20">
       <c r="A117" s="1" t="s">
@@ -4982,30 +3587,14 @@
       <c r="B117" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M117" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="N117" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="O117" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P117" s="12">
-        <v>7</v>
-      </c>
-      <c r="Q117" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R117" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S117" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T117" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="M117" s="8"/>
+      <c r="N117" s="12"/>
+      <c r="O117" s="12"/>
+      <c r="P117" s="12"/>
+      <c r="Q117" s="12"/>
+      <c r="R117" s="12"/>
+      <c r="S117" s="8"/>
+      <c r="T117" s="8"/>
     </row>
     <row r="118" spans="1:20">
       <c r="A118" s="1" t="s">
@@ -5014,30 +3603,14 @@
       <c r="B118" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M118" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="N118" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="O118" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P118" s="12">
-        <v>20</v>
-      </c>
-      <c r="Q118" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R118" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S118" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T118" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="M118" s="8"/>
+      <c r="N118" s="12"/>
+      <c r="O118" s="12"/>
+      <c r="P118" s="12"/>
+      <c r="Q118" s="12"/>
+      <c r="R118" s="12"/>
+      <c r="S118" s="8"/>
+      <c r="T118" s="8"/>
     </row>
     <row r="119" spans="1:20">
       <c r="A119" s="1" t="s">
@@ -5046,30 +3619,14 @@
       <c r="B119" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="M119" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="N119" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="O119" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P119" s="12">
-        <v>18</v>
-      </c>
-      <c r="Q119" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R119" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S119" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T119" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="M119" s="8"/>
+      <c r="N119" s="12"/>
+      <c r="O119" s="12"/>
+      <c r="P119" s="12"/>
+      <c r="Q119" s="12"/>
+      <c r="R119" s="12"/>
+      <c r="S119" s="8"/>
+      <c r="T119" s="8"/>
     </row>
     <row r="120" spans="1:20">
       <c r="A120" s="1" t="s">
@@ -5078,30 +3635,14 @@
       <c r="B120" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M120" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="N120" s="12" t="s">
-        <v>355</v>
-      </c>
-      <c r="O120" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P120" s="12">
-        <v>6</v>
-      </c>
-      <c r="Q120" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R120" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S120" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T120" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="M120" s="8"/>
+      <c r="N120" s="12"/>
+      <c r="O120" s="12"/>
+      <c r="P120" s="12"/>
+      <c r="Q120" s="12"/>
+      <c r="R120" s="12"/>
+      <c r="S120" s="8"/>
+      <c r="T120" s="8"/>
     </row>
     <row r="121" spans="1:20">
       <c r="A121" s="1" t="s">
@@ -5110,30 +3651,14 @@
       <c r="B121" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M121" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="N121" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="O121" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="P121" s="12">
-        <v>6</v>
-      </c>
-      <c r="Q121" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R121" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S121" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="T121" s="2" t="s">
-        <v>115</v>
-      </c>
+      <c r="M121" s="8"/>
+      <c r="N121" s="12"/>
+      <c r="O121" s="12"/>
+      <c r="P121" s="12"/>
+      <c r="Q121" s="12"/>
+      <c r="R121" s="12"/>
+      <c r="S121" s="8"/>
+      <c r="T121" s="8"/>
     </row>
     <row r="122" spans="1:20">
       <c r="A122" s="1" t="s">
@@ -5142,30 +3667,14 @@
       <c r="B122" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M122" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="N122" s="12" t="s">
-        <v>357</v>
-      </c>
-      <c r="O122" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P122" s="12">
-        <v>36</v>
-      </c>
-      <c r="Q122" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R122" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S122" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T122" s="12" t="s">
-        <v>143</v>
-      </c>
+      <c r="M122" s="8"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
+      <c r="R122" s="12"/>
+      <c r="S122" s="8"/>
+      <c r="T122" s="12"/>
     </row>
     <row r="123" spans="1:20">
       <c r="A123" s="1" t="s">
@@ -5174,30 +3683,14 @@
       <c r="B123" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M123" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="N123" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="O123" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P123" s="12">
-        <v>38</v>
-      </c>
-      <c r="Q123" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R123" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S123" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T123" s="12" t="s">
-        <v>143</v>
-      </c>
+      <c r="M123" s="8"/>
+      <c r="N123" s="12"/>
+      <c r="O123" s="12"/>
+      <c r="P123" s="12"/>
+      <c r="Q123" s="12"/>
+      <c r="R123" s="12"/>
+      <c r="S123" s="8"/>
+      <c r="T123" s="12"/>
     </row>
     <row r="124" spans="1:20">
       <c r="A124" s="1" t="s">
@@ -5206,30 +3699,14 @@
       <c r="B124" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="M124" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="N124" s="12" t="s">
-        <v>359</v>
-      </c>
-      <c r="O124" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P124" s="12">
-        <v>40</v>
-      </c>
-      <c r="Q124" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R124" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S124" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T124" s="12" t="s">
-        <v>143</v>
-      </c>
+      <c r="M124" s="8"/>
+      <c r="N124" s="12"/>
+      <c r="O124" s="12"/>
+      <c r="P124" s="12"/>
+      <c r="Q124" s="12"/>
+      <c r="R124" s="12"/>
+      <c r="S124" s="8"/>
+      <c r="T124" s="12"/>
     </row>
     <row r="125" spans="1:20">
       <c r="A125" s="1" t="s">
@@ -5238,30 +3715,14 @@
       <c r="B125" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="M125" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="N125" s="12" t="s">
-        <v>360</v>
-      </c>
-      <c r="O125" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P125" s="12">
-        <v>38</v>
-      </c>
-      <c r="Q125" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R125" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S125" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T125" s="12" t="s">
-        <v>143</v>
-      </c>
+      <c r="M125" s="8"/>
+      <c r="N125" s="12"/>
+      <c r="O125" s="12"/>
+      <c r="P125" s="12"/>
+      <c r="Q125" s="12"/>
+      <c r="R125" s="12"/>
+      <c r="S125" s="8"/>
+      <c r="T125" s="12"/>
     </row>
     <row r="126" spans="1:20">
       <c r="A126" s="1" t="s">
@@ -5270,30 +3731,14 @@
       <c r="B126" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="M126" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="N126" s="12" t="s">
-        <v>361</v>
-      </c>
-      <c r="O126" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P126" s="12">
-        <v>40</v>
-      </c>
-      <c r="Q126" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R126" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S126" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T126" s="12" t="s">
-        <v>143</v>
-      </c>
+      <c r="M126" s="8"/>
+      <c r="N126" s="12"/>
+      <c r="O126" s="12"/>
+      <c r="P126" s="12"/>
+      <c r="Q126" s="12"/>
+      <c r="R126" s="12"/>
+      <c r="S126" s="8"/>
+      <c r="T126" s="12"/>
     </row>
     <row r="127" spans="1:20">
       <c r="A127" s="1" t="s">
@@ -5302,30 +3747,14 @@
       <c r="B127" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="M127" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="N127" s="12" t="s">
-        <v>362</v>
-      </c>
-      <c r="O127" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P127" s="12">
-        <v>39</v>
-      </c>
-      <c r="Q127" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R127" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S127" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T127" s="12" t="s">
-        <v>143</v>
-      </c>
+      <c r="M127" s="8"/>
+      <c r="N127" s="12"/>
+      <c r="O127" s="12"/>
+      <c r="P127" s="12"/>
+      <c r="Q127" s="12"/>
+      <c r="R127" s="12"/>
+      <c r="S127" s="8"/>
+      <c r="T127" s="12"/>
     </row>
     <row r="128" spans="1:20">
       <c r="A128" s="1" t="s">
@@ -5334,30 +3763,14 @@
       <c r="B128" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="M128" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="N128" s="12" t="s">
-        <v>364</v>
-      </c>
-      <c r="O128" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="P128" s="12">
-        <v>10</v>
-      </c>
-      <c r="Q128" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R128" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S128" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="T128" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="M128" s="8"/>
+      <c r="N128" s="12"/>
+      <c r="O128" s="8"/>
+      <c r="P128" s="12"/>
+      <c r="Q128" s="12"/>
+      <c r="R128" s="12"/>
+      <c r="S128" s="8"/>
+      <c r="T128" s="8"/>
     </row>
     <row r="129" spans="1:20">
       <c r="A129" s="1" t="s">
@@ -5366,30 +3779,14 @@
       <c r="B129" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="M129" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="N129" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="O129" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="P129" s="12">
-        <v>12</v>
-      </c>
-      <c r="Q129" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R129" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S129" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="T129" s="2" t="s">
-        <v>133</v>
-      </c>
+      <c r="M129" s="8"/>
+      <c r="N129" s="8"/>
+      <c r="O129" s="8"/>
+      <c r="P129" s="12"/>
+      <c r="Q129" s="12"/>
+      <c r="R129" s="12"/>
+      <c r="S129" s="8"/>
+      <c r="T129" s="8"/>
     </row>
     <row r="130" spans="1:20">
       <c r="A130" s="1" t="s">
@@ -6160,11 +4557,11 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17577034-6810-45EB-B138-D5219A90AFAB}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="11.109375" customWidth="1"/>
-    <col min="4" max="4" width="12.109375" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -6259,10 +4656,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF68DE72-AEE1-4ED0-BFF5-DFC6E78C7F67}">
   <dimension ref="A1:B39"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="40.5546875" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" customWidth="1"/>
+    <col min="1" max="1" width="40.5703125" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -6586,16 +4983,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C89F0278-9583-4842-A27E-70B7F705F4F8}">
   <dimension ref="A1:H39"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
-    <col min="2" max="2" width="25.6640625" customWidth="1"/>
-    <col min="3" max="3" width="18.44140625" customWidth="1"/>
-    <col min="4" max="4" width="18.5546875" customWidth="1"/>
-    <col min="5" max="5" width="18.109375" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="18.42578125" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="23.7109375" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
-    <col min="8" max="8" width="55.88671875" customWidth="1"/>
+    <col min="8" max="8" width="55.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -7257,10 +5654,10 @@
       <c r="A39" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="B39" s="12" t="s">
+      <c r="B39" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="2">
         <v>5</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -7278,16 +5675,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60D70A01-E011-4D5C-AF4A-BF7940E4CD9E}">
-  <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="38.5546875" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="38.5703125" customWidth="1"/>
+    <col min="2" max="2" width="15.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7300,8 +5698,11 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" s="2" t="s">
         <v>101</v>
       </c>
@@ -7314,8 +5715,11 @@
       <c r="D2" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
         <v>111</v>
       </c>
@@ -7328,8 +5732,11 @@
       <c r="D3" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
         <v>112</v>
       </c>
@@ -7342,8 +5749,11 @@
       <c r="D4" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="2" t="s">
         <v>113</v>
       </c>
@@ -7356,8 +5766,11 @@
       <c r="D5" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="2" t="s">
         <v>114</v>
       </c>
@@ -7370,8 +5783,11 @@
       <c r="D6" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
         <v>115</v>
       </c>
@@ -7384,8 +5800,11 @@
       <c r="D7" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="E7" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="6" t="s">
         <v>116</v>
       </c>
@@ -7398,8 +5817,11 @@
       <c r="D8" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
         <v>117</v>
       </c>
@@ -7412,8 +5834,11 @@
       <c r="D9" s="2" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="2" t="s">
         <v>118</v>
       </c>
@@ -7425,6 +5850,9 @@
       </c>
       <c r="D10" s="2" t="s">
         <v>65</v>
+      </c>
+      <c r="E10" s="2">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -7434,17 +5862,18 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7799660A-6A70-4E53-ADA2-AEC7FFF55C28}">
-  <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.5546875" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
-    <col min="3" max="3" width="9.88671875" customWidth="1"/>
-    <col min="4" max="4" width="9.5546875" customWidth="1"/>
-    <col min="5" max="5" width="34.88671875" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.5703125" customWidth="1"/>
+    <col min="5" max="5" width="34.85546875" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7460,8 +5889,11 @@
       <c r="E1" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="20" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>128</v>
       </c>
@@ -7477,8 +5909,11 @@
       <c r="E2" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
         <v>129</v>
       </c>
@@ -7494,8 +5929,11 @@
       <c r="E3" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
         <v>130</v>
       </c>
@@ -7511,8 +5949,11 @@
       <c r="E4" s="2" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
         <v>131</v>
       </c>
@@ -7528,8 +5969,11 @@
       <c r="E5" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
         <v>132</v>
       </c>
@@ -7545,8 +5989,11 @@
       <c r="E6" s="2" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
         <v>133</v>
       </c>
@@ -7562,8 +6009,11 @@
       <c r="E7" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
         <v>134</v>
       </c>
@@ -7579,8 +6029,11 @@
       <c r="E8" s="2" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
         <v>135</v>
       </c>
@@ -7595,6 +6048,9 @@
       </c>
       <c r="E9" s="2" t="s">
         <v>118</v>
+      </c>
+      <c r="F9" s="21">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -7604,19 +6060,20 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA2111D6-4486-49FF-8151-BCB73604576D}">
-  <dimension ref="A1:H77"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:I77"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.88671875" customWidth="1"/>
-    <col min="2" max="2" width="25.44140625" customWidth="1"/>
-    <col min="3" max="3" width="33.44140625" customWidth="1"/>
-    <col min="5" max="5" width="9.44140625" customWidth="1"/>
-    <col min="6" max="6" width="9.88671875" customWidth="1"/>
-    <col min="7" max="7" width="36.6640625" customWidth="1"/>
-    <col min="8" max="8" width="35.88671875" customWidth="1"/>
+    <col min="1" max="1" width="37.85546875" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="33.42578125" customWidth="1"/>
+    <col min="5" max="5" width="9.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.85546875" customWidth="1"/>
+    <col min="7" max="7" width="36.7109375" customWidth="1"/>
+    <col min="8" max="8" width="35.85546875" customWidth="1"/>
+    <col min="9" max="9" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7641,8 +6098,11 @@
       <c r="H1" s="1" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="19" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>144</v>
       </c>
@@ -7667,8 +6127,11 @@
       <c r="H2" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>145</v>
       </c>
@@ -7693,8 +6156,11 @@
       <c r="H3" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>146</v>
       </c>
@@ -7719,8 +6185,11 @@
       <c r="H4" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>147</v>
       </c>
@@ -7745,8 +6214,11 @@
       <c r="H5" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>148</v>
       </c>
@@ -7771,8 +6243,11 @@
       <c r="H6" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>149</v>
       </c>
@@ -7797,8 +6272,11 @@
       <c r="H7" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
         <v>150</v>
       </c>
@@ -7823,8 +6301,11 @@
       <c r="H8" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
         <v>151</v>
       </c>
@@ -7849,8 +6330,11 @@
       <c r="H9" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
         <v>152</v>
       </c>
@@ -7875,8 +6359,11 @@
       <c r="H10" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="2">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
         <v>153</v>
       </c>
@@ -7901,8 +6388,11 @@
       <c r="H11" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
         <v>154</v>
       </c>
@@ -7927,8 +6417,11 @@
       <c r="H12" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="2">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
         <v>155</v>
       </c>
@@ -7953,8 +6446,11 @@
       <c r="H13" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
         <v>156</v>
       </c>
@@ -7979,8 +6475,11 @@
       <c r="H14" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="2">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
         <v>157</v>
       </c>
@@ -8005,8 +6504,11 @@
       <c r="H15" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
         <v>158</v>
       </c>
@@ -8031,8 +6533,11 @@
       <c r="H16" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="1" t="s">
         <v>159</v>
       </c>
@@ -8057,8 +6562,11 @@
       <c r="H17" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="1" t="s">
         <v>160</v>
       </c>
@@ -8083,8 +6591,11 @@
       <c r="H18" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="1" t="s">
         <v>161</v>
       </c>
@@ -8109,8 +6620,11 @@
       <c r="H19" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="1" t="s">
         <v>162</v>
       </c>
@@ -8135,8 +6649,11 @@
       <c r="H20" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="1" t="s">
         <v>163</v>
       </c>
@@ -8161,8 +6678,11 @@
       <c r="H21" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="1" t="s">
         <v>164</v>
       </c>
@@ -8187,8 +6707,11 @@
       <c r="H22" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="1" t="s">
         <v>165</v>
       </c>
@@ -8213,8 +6736,11 @@
       <c r="H23" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="1" t="s">
         <v>166</v>
       </c>
@@ -8239,8 +6765,11 @@
       <c r="H24" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="25" spans="1:8">
+      <c r="I24" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="1" t="s">
         <v>167</v>
       </c>
@@ -8265,8 +6794,11 @@
       <c r="H25" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="26" spans="1:8">
+      <c r="I25" s="2">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
         <v>168</v>
       </c>
@@ -8291,8 +6823,11 @@
       <c r="H26" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="27" spans="1:8">
+      <c r="I26" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
         <v>169</v>
       </c>
@@ -8317,8 +6852,11 @@
       <c r="H27" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="28" spans="1:8">
+      <c r="I27" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
         <v>170</v>
       </c>
@@ -8343,8 +6881,11 @@
       <c r="H28" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="29" spans="1:8">
+      <c r="I28" s="2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
         <v>171</v>
       </c>
@@ -8369,8 +6910,11 @@
       <c r="H29" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="30" spans="1:8">
+      <c r="I29" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
         <v>172</v>
       </c>
@@ -8395,8 +6939,11 @@
       <c r="H30" s="1" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="31" spans="1:8">
+      <c r="I30" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
         <v>173</v>
       </c>
@@ -8421,8 +6968,11 @@
       <c r="H31" s="1" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="32" spans="1:8">
+      <c r="I31" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
         <v>174</v>
       </c>
@@ -8447,8 +6997,11 @@
       <c r="H32" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="33" spans="1:8">
+      <c r="I32" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
       <c r="A33" s="1" t="s">
         <v>175</v>
       </c>
@@ -8473,8 +7026,11 @@
       <c r="H33" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="34" spans="1:8">
+      <c r="I33" s="2">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
       <c r="A34" s="1" t="s">
         <v>176</v>
       </c>
@@ -8499,8 +7055,11 @@
       <c r="H34" s="1" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="35" spans="1:8">
+      <c r="I34" s="2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
       <c r="A35" s="1" t="s">
         <v>177</v>
       </c>
@@ -8525,8 +7084,11 @@
       <c r="H35" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="36" spans="1:8">
+      <c r="I35" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
       <c r="A36" s="1" t="s">
         <v>178</v>
       </c>
@@ -8551,8 +7113,11 @@
       <c r="H36" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="37" spans="1:8">
+      <c r="I36" s="2">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
       <c r="A37" s="1" t="s">
         <v>179</v>
       </c>
@@ -8577,8 +7142,11 @@
       <c r="H37" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="38" spans="1:8">
+      <c r="I37" s="2">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
         <v>180</v>
       </c>
@@ -8603,8 +7171,11 @@
       <c r="H38" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="39" spans="1:8">
+      <c r="I38" s="2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
         <v>181</v>
       </c>
@@ -8629,8 +7200,11 @@
       <c r="H39" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="40" spans="1:8">
+      <c r="I39" s="2">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
         <v>182</v>
       </c>
@@ -8655,8 +7229,11 @@
       <c r="H40" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="41" spans="1:8">
+      <c r="I40" s="2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
       <c r="A41" s="1" t="s">
         <v>183</v>
       </c>
@@ -8681,8 +7258,11 @@
       <c r="H41" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="42" spans="1:8">
+      <c r="I41" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
       <c r="A42" s="1" t="s">
         <v>184</v>
       </c>
@@ -8707,8 +7287,11 @@
       <c r="H42" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="43" spans="1:8">
+      <c r="I42" s="2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
       <c r="A43" s="2" t="s">
         <v>187</v>
       </c>
@@ -8733,8 +7316,11 @@
       <c r="H43" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="44" spans="1:8">
+      <c r="I43" s="2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
       <c r="A44" s="2" t="s">
         <v>188</v>
       </c>
@@ -8759,8 +7345,11 @@
       <c r="H44" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="45" spans="1:8">
+      <c r="I44" s="2">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
       <c r="A45" s="2" t="s">
         <v>189</v>
       </c>
@@ -8785,8 +7374,11 @@
       <c r="H45" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="46" spans="1:8">
+      <c r="I45" s="2">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
       <c r="A46" s="2" t="s">
         <v>190</v>
       </c>
@@ -8811,8 +7403,11 @@
       <c r="H46" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="47" spans="1:8">
+      <c r="I46" s="2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
       <c r="A47" s="2" t="s">
         <v>191</v>
       </c>
@@ -8837,8 +7432,11 @@
       <c r="H47" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="48" spans="1:8">
+      <c r="I47" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
       <c r="A48" s="2" t="s">
         <v>192</v>
       </c>
@@ -8863,8 +7461,11 @@
       <c r="H48" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="I48" s="2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
       <c r="A49" s="2" t="s">
         <v>195</v>
       </c>
@@ -8889,8 +7490,11 @@
       <c r="H49" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="I49" s="2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
       <c r="A50" s="14" t="s">
         <v>196</v>
       </c>
@@ -8915,18 +7519,21 @@
       <c r="H50" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="I50" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
       <c r="A51" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B51" s="12" t="s">
+      <c r="B51" s="1" t="s">
         <v>338</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D51" s="12">
+      <c r="D51" s="1">
         <v>16</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -8941,18 +7548,21 @@
       <c r="H51" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="52" spans="1:8">
+      <c r="I51" s="2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
       <c r="A52" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="B52" s="12" t="s">
+      <c r="B52" s="1" t="s">
         <v>339</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D52" s="12">
+      <c r="D52" s="1">
         <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -8967,18 +7577,21 @@
       <c r="H52" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="I52" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
       <c r="A53" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B53" s="12" t="s">
+      <c r="B53" s="1" t="s">
         <v>340</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D53" s="12">
+      <c r="D53" s="1">
         <v>18</v>
       </c>
       <c r="E53" s="1" t="s">
@@ -8993,18 +7606,21 @@
       <c r="H53" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="I53" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B54" s="12" t="s">
+      <c r="B54" s="1" t="s">
         <v>341</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D54" s="12">
+      <c r="D54" s="1">
         <v>18</v>
       </c>
       <c r="E54" s="1" t="s">
@@ -9019,18 +7635,21 @@
       <c r="H54" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="I54" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B55" s="12" t="s">
+      <c r="B55" s="1" t="s">
         <v>342</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D55" s="1">
         <v>12</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -9045,18 +7664,21 @@
       <c r="H55" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="I55" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
       <c r="A56" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="B56" s="12" t="s">
+      <c r="B56" s="1" t="s">
         <v>343</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D56" s="12">
+      <c r="D56" s="1">
         <v>12</v>
       </c>
       <c r="E56" s="1" t="s">
@@ -9071,18 +7693,21 @@
       <c r="H56" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="I56" s="2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
       <c r="A57" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B57" s="12" t="s">
+      <c r="B57" s="1" t="s">
         <v>344</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D57" s="12">
+      <c r="D57" s="1">
         <v>10</v>
       </c>
       <c r="E57" s="1" t="s">
@@ -9094,21 +7719,24 @@
       <c r="G57" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="H57" s="12" t="s">
+      <c r="H57" s="1" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="I57" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="B58" s="12" t="s">
+      <c r="B58" s="1" t="s">
         <v>345</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D58" s="12">
+      <c r="D58" s="1">
         <v>12</v>
       </c>
       <c r="E58" s="1" t="s">
@@ -9123,18 +7751,21 @@
       <c r="H58" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="I58" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
       <c r="A59" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="1" t="s">
         <v>346</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D59" s="12">
+      <c r="D59" s="1">
         <v>7</v>
       </c>
       <c r="E59" s="1" t="s">
@@ -9149,18 +7780,21 @@
       <c r="H59" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="60" spans="1:8">
+      <c r="I59" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
       <c r="A60" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B60" s="12" t="s">
+      <c r="B60" s="1" t="s">
         <v>347</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D60" s="12">
+      <c r="D60" s="1">
         <v>10</v>
       </c>
       <c r="E60" s="1" t="s">
@@ -9175,8 +7809,11 @@
       <c r="H60" s="2" t="s">
         <v>131</v>
       </c>
-    </row>
-    <row r="61" spans="1:8">
+      <c r="I60" s="2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
       <c r="A61" s="2" t="s">
         <v>378</v>
       </c>
@@ -9186,7 +7823,7 @@
       <c r="C61" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D61" s="12">
+      <c r="D61" s="1">
         <v>12</v>
       </c>
       <c r="E61" s="1" t="s">
@@ -9201,8 +7838,11 @@
       <c r="H61" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="62" spans="1:8">
+      <c r="I61" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
       <c r="A62" s="2" t="s">
         <v>379</v>
       </c>
@@ -9212,7 +7852,7 @@
       <c r="C62" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D62" s="12">
+      <c r="D62" s="1">
         <v>10</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -9227,18 +7867,21 @@
       <c r="H62" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="63" spans="1:8">
+      <c r="I62" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
       <c r="A63" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B63" s="12" t="s">
+      <c r="B63" s="1" t="s">
         <v>363</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D63" s="12">
+      <c r="D63" s="1">
         <v>10</v>
       </c>
       <c r="E63" s="1" t="s">
@@ -9253,18 +7896,21 @@
       <c r="H63" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="64" spans="1:8">
+      <c r="I63" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
       <c r="A64" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="B64" s="12" t="s">
+      <c r="B64" s="1" t="s">
         <v>351</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D64" s="12">
+      <c r="D64" s="1">
         <v>10</v>
       </c>
       <c r="E64" s="1" t="s">
@@ -9279,18 +7925,21 @@
       <c r="H64" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="65" spans="1:8">
+      <c r="I64" s="2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
       <c r="A65" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B65" s="12" t="s">
+      <c r="B65" s="1" t="s">
         <v>352</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D65" s="12">
+      <c r="D65" s="1">
         <v>7</v>
       </c>
       <c r="E65" s="1" t="s">
@@ -9305,18 +7954,21 @@
       <c r="H65" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="I65" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="B66" s="12" t="s">
+      <c r="B66" s="1" t="s">
         <v>353</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D66" s="12">
+      <c r="D66" s="1">
         <v>20</v>
       </c>
       <c r="E66" s="1" t="s">
@@ -9331,18 +7983,21 @@
       <c r="H66" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="I66" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="B67" s="12" t="s">
+      <c r="B67" s="1" t="s">
         <v>354</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D67" s="12">
+      <c r="D67" s="1">
         <v>18</v>
       </c>
       <c r="E67" s="1" t="s">
@@ -9357,18 +8012,21 @@
       <c r="H67" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="I67" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B68" s="12" t="s">
+      <c r="B68" s="1" t="s">
         <v>355</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D68" s="12">
+      <c r="D68" s="1">
         <v>6</v>
       </c>
       <c r="E68" s="1" t="s">
@@ -9383,18 +8041,21 @@
       <c r="H68" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="69" spans="1:8">
+      <c r="I68" s="2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="B69" s="12" t="s">
+      <c r="B69" s="1" t="s">
         <v>356</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D69" s="12">
+      <c r="D69" s="1">
         <v>6</v>
       </c>
       <c r="E69" s="1" t="s">
@@ -9409,18 +8070,21 @@
       <c r="H69" s="2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="70" spans="1:8">
+      <c r="I69" s="2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="B70" s="12" t="s">
+      <c r="B70" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="C70" s="12" t="s">
+      <c r="C70" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D70" s="12">
+      <c r="D70" s="1">
         <v>36</v>
       </c>
       <c r="E70" s="1" t="s">
@@ -9432,21 +8096,24 @@
       <c r="G70" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H70" s="12" t="s">
+      <c r="H70" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="71" spans="1:8">
+      <c r="I70" s="2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B71" s="12" t="s">
+      <c r="B71" s="1" t="s">
         <v>358</v>
       </c>
-      <c r="C71" s="12" t="s">
+      <c r="C71" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D71" s="12">
+      <c r="D71" s="1">
         <v>38</v>
       </c>
       <c r="E71" s="1" t="s">
@@ -9458,21 +8125,24 @@
       <c r="G71" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H71" s="12" t="s">
+      <c r="H71" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="72" spans="1:8">
+      <c r="I71" s="2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
       <c r="A72" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B72" s="12" t="s">
+      <c r="B72" s="1" t="s">
         <v>359</v>
       </c>
-      <c r="C72" s="12" t="s">
+      <c r="C72" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D72" s="12">
+      <c r="D72" s="1">
         <v>40</v>
       </c>
       <c r="E72" s="1" t="s">
@@ -9484,21 +8154,24 @@
       <c r="G72" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H72" s="12" t="s">
+      <c r="H72" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="73" spans="1:8">
+      <c r="I72" s="2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
       <c r="A73" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="B73" s="12" t="s">
+      <c r="B73" s="1" t="s">
         <v>360</v>
       </c>
-      <c r="C73" s="12" t="s">
+      <c r="C73" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D73" s="12">
+      <c r="D73" s="1">
         <v>38</v>
       </c>
       <c r="E73" s="1" t="s">
@@ -9510,21 +8183,24 @@
       <c r="G73" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H73" s="12" t="s">
+      <c r="H73" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="74" spans="1:8">
+      <c r="I73" s="2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
       <c r="A74" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="B74" s="12" t="s">
+      <c r="B74" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="C74" s="12" t="s">
+      <c r="C74" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D74" s="12">
+      <c r="D74" s="1">
         <v>40</v>
       </c>
       <c r="E74" s="1" t="s">
@@ -9536,21 +8212,24 @@
       <c r="G74" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H74" s="12" t="s">
+      <c r="H74" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="75" spans="1:8">
+      <c r="I74" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
       <c r="A75" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="B75" s="12" t="s">
+      <c r="B75" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C75" s="12" t="s">
+      <c r="C75" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="D75" s="12">
+      <c r="D75" s="1">
         <v>39</v>
       </c>
       <c r="E75" s="1" t="s">
@@ -9562,21 +8241,24 @@
       <c r="G75" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="H75" s="12" t="s">
+      <c r="H75" s="1" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="76" spans="1:8">
+      <c r="I75" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
       <c r="A76" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B76" s="12" t="s">
+      <c r="B76" s="1" t="s">
         <v>364</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D76" s="12">
+      <c r="D76" s="1">
         <v>10</v>
       </c>
       <c r="E76" s="1" t="s">
@@ -9591,8 +8273,11 @@
       <c r="H76" s="2" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="77" spans="1:8">
+      <c r="I76" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
       <c r="A77" s="2" t="s">
         <v>394</v>
       </c>
@@ -9602,7 +8287,7 @@
       <c r="C77" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D77" s="12">
+      <c r="D77" s="1">
         <v>12</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -9616,6 +8301,9 @@
       </c>
       <c r="H77" s="2" t="s">
         <v>133</v>
+      </c>
+      <c r="I77" s="2">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -9627,14 +8315,14 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{256B2A91-27AB-4BC1-A1F0-115B786A674D}">
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="37.109375" customWidth="1"/>
+    <col min="1" max="1" width="37.140625" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
     <col min="3" max="4" width="11" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="15.44140625" customWidth="1"/>
-    <col min="7" max="7" width="38.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" customWidth="1"/>
+    <col min="7" max="7" width="38.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -10151,9 +8839,9 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEDC361-D738-4510-89A2-AB67CB12EBDF}">
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.88671875" customWidth="1"/>
+    <col min="1" max="1" width="36.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10276,14 +8964,14 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F05608C-89F7-443B-8F02-A238CB7CF577}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="38.88671875" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="1" max="1" width="38.85546875" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" customWidth="1"/>
-    <col min="7" max="7" width="36.44140625" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11.85546875" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
@@ -10363,12 +9051,12 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C9E1B61-911D-4E67-9431-CC6DC22C7D98}">
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="36.5546875" customWidth="1"/>
+    <col min="1" max="1" width="36.5703125" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
-    <col min="6" max="6" width="36.5546875" customWidth="1"/>
-    <col min="7" max="7" width="35.5546875" customWidth="1"/>
+    <col min="6" max="6" width="36.5703125" customWidth="1"/>
+    <col min="7" max="7" width="35.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">

--- a/backend/API/SeedData.xlsx
+++ b/backend/API/SeedData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jakub\Desktop\Cs\pc\RestaurantOrderingAppSolution\backend\API\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Piccolo\RestaurantOrderingAppSolution\backend\API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E014274-5C7C-4C20-8514-8C45313A6EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCD072AE-DC05-44C4-8831-126886657FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="4" xr2:uid="{C8CF7BA1-E9AA-4852-A9EB-5F1AD6BFABCB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="12" xr2:uid="{C8CF7BA1-E9AA-4852-A9EB-5F1AD6BFABCB}"/>
   </bookViews>
   <sheets>
     <sheet name="CustomerInformation" sheetId="1" r:id="rId1"/>
@@ -19,12 +19,12 @@
     <sheet name="SubCategory" sheetId="4" r:id="rId4"/>
     <sheet name="MenuItem" sheetId="5" r:id="rId5"/>
     <sheet name="Table" sheetId="7" r:id="rId6"/>
-    <sheet name="Tag" sheetId="8" r:id="rId7"/>
-    <sheet name="Reservation" sheetId="9" r:id="rId8"/>
-    <sheet name="OrderItem" sheetId="10" r:id="rId9"/>
-    <sheet name="Order" sheetId="11" r:id="rId10"/>
-    <sheet name="MenuItemIngredientRel" sheetId="6" r:id="rId11"/>
-    <sheet name="Area" sheetId="13" r:id="rId12"/>
+    <sheet name="Reservation" sheetId="9" r:id="rId7"/>
+    <sheet name="OrderItem" sheetId="10" r:id="rId8"/>
+    <sheet name="Order" sheetId="11" r:id="rId9"/>
+    <sheet name="MenuItemIngredientRel" sheetId="6" r:id="rId10"/>
+    <sheet name="Area" sheetId="13" r:id="rId11"/>
+    <sheet name="Tag" sheetId="8" r:id="rId12"/>
     <sheet name="IngredientTagRel" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="385">
   <si>
     <t>Id</t>
   </si>
@@ -856,45 +856,6 @@
   </si>
   <si>
     <t>TagId</t>
-  </si>
-  <si>
-    <t>e3e07ec9-75f1-45bb-b435-7ab002a68b74</t>
-  </si>
-  <si>
-    <t>e3e07ec9-75f1-45bb-b435-7ab002a68b75</t>
-  </si>
-  <si>
-    <t>e3e07ec9-75f1-45bb-b435-7ab002a68b76</t>
-  </si>
-  <si>
-    <t>e3e07ec9-75f1-45bb-b435-7ab002a68b77</t>
-  </si>
-  <si>
-    <t>15febb8e-5c89-4416-ac10-7011f7f31cd9</t>
-  </si>
-  <si>
-    <t>15febb8e-5c89-4416-ac10-7011f7f31cd10</t>
-  </si>
-  <si>
-    <t>15febb8e-5c89-4416-ac10-7011f7f31cd11</t>
-  </si>
-  <si>
-    <t>15febb8e-5c89-4416-ac10-7011f7f31cd12</t>
-  </si>
-  <si>
-    <t>66109b01-6f01-49e9-ab47-249eba53f078</t>
-  </si>
-  <si>
-    <t>66109b01-6f01-49e9-ab47-249eba53f079</t>
-  </si>
-  <si>
-    <t>66109b01-6f01-49e9-ab47-249eba53f080</t>
-  </si>
-  <si>
-    <t>66109b01-6f01-49e9-ab47-249eba53f081</t>
-  </si>
-  <si>
-    <t>66109b01-6f01-49e9-ab47-249eba53f082</t>
   </si>
   <si>
     <t>5ecdc81b-929e-4ee9-b82d-8a7d4f3218a6</t>
@@ -1316,7 +1277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1372,12 +1333,6 @@
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1397,9 +1352,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motyw pakietu Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Pakiet Office">
+    <a:clrScheme name="Pakiet Office 2013–2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1437,7 +1392,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Pakiet Office">
+    <a:fontScheme name="Pakiet Office 2013–2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1543,7 +1498,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Pakiet Office">
+    <a:fmtScheme name="Pakiet Office 2013–2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1685,7 +1640,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1795,141 +1750,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4966BB-B585-4EFD-A171-2B6D26A10B97}">
-  <dimension ref="A1:I4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="36.5703125" customWidth="1"/>
-    <col min="2" max="2" width="23.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" customWidth="1"/>
-    <col min="8" max="8" width="37.42578125" customWidth="1"/>
-    <col min="9" max="9" width="36.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="10">
-        <v>45726.604166666664</v>
-      </c>
-      <c r="C2" s="2">
-        <v>30</v>
-      </c>
-      <c r="D2" s="2">
-        <v>0</v>
-      </c>
-      <c r="E2" s="2">
-        <v>0</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="10">
-        <v>45757.618055555555</v>
-      </c>
-      <c r="C3" s="2">
-        <v>40</v>
-      </c>
-      <c r="D3" s="2">
-        <v>0</v>
-      </c>
-      <c r="E3" s="2">
-        <v>0</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B4" s="10">
-        <v>45758.618055555555</v>
-      </c>
-      <c r="C4" s="2">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2E4AC9-0CD2-4F25-AD3B-36A84397D079}">
   <dimension ref="A1:T224"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2144,7 +1964,7 @@
         <v>147</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="M19" s="8"/>
       <c r="N19" s="12"/>
@@ -2391,7 +2211,7 @@
         <v>150</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="M38" s="8"/>
       <c r="N38" s="12"/>
@@ -4270,7 +4090,7 @@
     </row>
     <row r="190" spans="1:2">
       <c r="A190" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>12</v>
@@ -4278,7 +4098,7 @@
     </row>
     <row r="191" spans="1:2">
       <c r="A191" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>66</v>
@@ -4286,7 +4106,7 @@
     </row>
     <row r="192" spans="1:2">
       <c r="A192" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>76</v>
@@ -4294,7 +4114,7 @@
     </row>
     <row r="193" spans="1:2">
       <c r="A193" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>85</v>
@@ -4302,7 +4122,7 @@
     </row>
     <row r="194" spans="1:2">
       <c r="A194" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>72</v>
@@ -4310,7 +4130,7 @@
     </row>
     <row r="195" spans="1:2">
       <c r="A195" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>70</v>
@@ -4318,7 +4138,7 @@
     </row>
     <row r="196" spans="1:2">
       <c r="A196" s="2" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>12</v>
@@ -4326,7 +4146,7 @@
     </row>
     <row r="197" spans="1:2">
       <c r="A197" s="2" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>66</v>
@@ -4334,7 +4154,7 @@
     </row>
     <row r="198" spans="1:2">
       <c r="A198" s="2" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>76</v>
@@ -4342,7 +4162,7 @@
     </row>
     <row r="199" spans="1:2">
       <c r="A199" s="2" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>77</v>
@@ -4350,7 +4170,7 @@
     </row>
     <row r="200" spans="1:2">
       <c r="A200" s="2" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>83</v>
@@ -4358,7 +4178,7 @@
     </row>
     <row r="201" spans="1:2">
       <c r="A201" s="2" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>90</v>
@@ -4366,7 +4186,7 @@
     </row>
     <row r="202" spans="1:2">
       <c r="A202" s="2" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>66</v>
@@ -4374,7 +4194,7 @@
     </row>
     <row r="203" spans="1:2">
       <c r="A203" s="2" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="B203" s="1" t="s">
         <v>11</v>
@@ -4382,7 +4202,7 @@
     </row>
     <row r="204" spans="1:2">
       <c r="A204" s="2" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>79</v>
@@ -4390,7 +4210,7 @@
     </row>
     <row r="205" spans="1:2">
       <c r="A205" s="2" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>88</v>
@@ -4398,7 +4218,7 @@
     </row>
     <row r="206" spans="1:2">
       <c r="A206" s="2" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>68</v>
@@ -4406,7 +4226,7 @@
     </row>
     <row r="207" spans="1:2">
       <c r="A207" s="2" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="B207" s="1" t="s">
         <v>12</v>
@@ -4414,7 +4234,7 @@
     </row>
     <row r="208" spans="1:2">
       <c r="A208" s="2" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>66</v>
@@ -4422,7 +4242,7 @@
     </row>
     <row r="209" spans="1:2">
       <c r="A209" s="2" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>80</v>
@@ -4430,7 +4250,7 @@
     </row>
     <row r="210" spans="1:2">
       <c r="A210" s="2" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>67</v>
@@ -4438,7 +4258,7 @@
     </row>
     <row r="211" spans="1:2">
       <c r="A211" s="2" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>84</v>
@@ -4446,7 +4266,7 @@
     </row>
     <row r="212" spans="1:2">
       <c r="A212" s="2" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>95</v>
@@ -4454,7 +4274,7 @@
     </row>
     <row r="213" spans="1:2">
       <c r="A213" s="2" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B213" s="1" t="s">
         <v>12</v>
@@ -4462,7 +4282,7 @@
     </row>
     <row r="214" spans="1:2">
       <c r="A214" s="2" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>66</v>
@@ -4470,7 +4290,7 @@
     </row>
     <row r="215" spans="1:2">
       <c r="A215" s="2" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>75</v>
@@ -4478,7 +4298,7 @@
     </row>
     <row r="216" spans="1:2">
       <c r="A216" s="2" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>87</v>
@@ -4486,7 +4306,7 @@
     </row>
     <row r="217" spans="1:2">
       <c r="A217" s="2" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>99</v>
@@ -4494,7 +4314,7 @@
     </row>
     <row r="218" spans="1:2">
       <c r="A218" s="2" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>73</v>
@@ -4502,7 +4322,7 @@
     </row>
     <row r="219" spans="1:2">
       <c r="A219" s="2" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="B219" s="1" t="s">
         <v>12</v>
@@ -4510,7 +4330,7 @@
     </row>
     <row r="220" spans="1:2">
       <c r="A220" s="2" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>66</v>
@@ -4518,7 +4338,7 @@
     </row>
     <row r="221" spans="1:2">
       <c r="A221" s="2" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>81</v>
@@ -4526,7 +4346,7 @@
     </row>
     <row r="222" spans="1:2">
       <c r="A222" s="2" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>83</v>
@@ -4534,7 +4354,7 @@
     </row>
     <row r="223" spans="1:2">
       <c r="A223" s="2" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>86</v>
@@ -4542,7 +4362,7 @@
     </row>
     <row r="224" spans="1:2">
       <c r="A224" s="2" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>96</v>
@@ -4554,7 +4374,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17577034-6810-45EB-B138-D5219A90AFAB}">
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4580,10 +4400,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>64</v>
@@ -4594,10 +4414,10 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>64</v>
@@ -4608,10 +4428,10 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>64</v>
@@ -4622,10 +4442,10 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>64</v>
@@ -4636,15 +4456,140 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEDC361-D738-4510-89A2-AB67CB12EBDF}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="41.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>65</v>
       </c>
     </row>
@@ -4739,7 +4684,7 @@
         <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4747,7 +4692,7 @@
         <v>73</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4811,7 +4756,7 @@
         <v>81</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>278</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4819,7 +4764,7 @@
         <v>82</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>279</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4827,7 +4772,7 @@
         <v>83</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4835,7 +4780,7 @@
         <v>84</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>281</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4843,7 +4788,7 @@
         <v>85</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>282</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -4899,7 +4844,7 @@
         <v>92</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>274</v>
+        <v>241</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -4907,7 +4852,7 @@
         <v>93</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>275</v>
+        <v>241</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -4915,7 +4860,7 @@
         <v>94</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>276</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -4923,7 +4868,7 @@
         <v>95</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>277</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -4939,7 +4884,7 @@
         <v>97</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>270</v>
+        <v>245</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -4947,7 +4892,7 @@
         <v>98</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>271</v>
+        <v>245</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -4955,7 +4900,7 @@
         <v>99</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>272</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -4963,12 +4908,12 @@
         <v>100</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>273</v>
+        <v>245</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>244</v>
@@ -5652,10 +5597,10 @@
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="2" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="C39" s="2">
         <v>5</v>
@@ -5699,7 +5644,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -5889,8 +5834,8 @@
       <c r="E1" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F1" s="20" t="s">
-        <v>397</v>
+      <c r="F1" s="2" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5909,7 +5854,7 @@
       <c r="E2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F2" s="21">
+      <c r="F2" s="19">
         <v>1</v>
       </c>
     </row>
@@ -5929,7 +5874,7 @@
       <c r="E3" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F3" s="21">
+      <c r="F3" s="19">
         <v>2</v>
       </c>
     </row>
@@ -5949,7 +5894,7 @@
       <c r="E4" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F4" s="21">
+      <c r="F4" s="19">
         <v>3</v>
       </c>
     </row>
@@ -5969,7 +5914,7 @@
       <c r="E5" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F5" s="21">
+      <c r="F5" s="19">
         <v>4</v>
       </c>
     </row>
@@ -5989,7 +5934,7 @@
       <c r="E6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="19">
         <v>5</v>
       </c>
     </row>
@@ -6009,7 +5954,7 @@
       <c r="E7" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="19">
         <v>6</v>
       </c>
     </row>
@@ -6029,7 +5974,7 @@
       <c r="E8" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="19">
         <v>7</v>
       </c>
     </row>
@@ -6049,7 +5994,7 @@
       <c r="E9" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="19">
         <v>8</v>
       </c>
     </row>
@@ -6098,8 +6043,8 @@
       <c r="H1" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="I1" s="19" t="s">
-        <v>397</v>
+      <c r="I1" s="1" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -6107,7 +6052,7 @@
         <v>144</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>185</v>
@@ -6136,7 +6081,7 @@
         <v>145</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>185</v>
@@ -6165,7 +6110,7 @@
         <v>146</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>185</v>
@@ -6194,7 +6139,7 @@
         <v>147</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>185</v>
@@ -6223,7 +6168,7 @@
         <v>148</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>185</v>
@@ -6252,7 +6197,7 @@
         <v>149</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>185</v>
@@ -6281,7 +6226,7 @@
         <v>150</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>185</v>
@@ -6310,7 +6255,7 @@
         <v>151</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>185</v>
@@ -6339,7 +6284,7 @@
         <v>152</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>185</v>
@@ -6368,7 +6313,7 @@
         <v>153</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>185</v>
@@ -6397,7 +6342,7 @@
         <v>154</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>185</v>
@@ -6426,7 +6371,7 @@
         <v>155</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>185</v>
@@ -6455,7 +6400,7 @@
         <v>156</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>185</v>
@@ -6484,7 +6429,7 @@
         <v>157</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>185</v>
@@ -6513,7 +6458,7 @@
         <v>158</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>185</v>
@@ -6542,7 +6487,7 @@
         <v>159</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>185</v>
@@ -6571,7 +6516,7 @@
         <v>160</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>185</v>
@@ -6600,7 +6545,7 @@
         <v>161</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>185</v>
@@ -6629,7 +6574,7 @@
         <v>162</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>185</v>
@@ -6658,7 +6603,7 @@
         <v>163</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>185</v>
@@ -6687,7 +6632,7 @@
         <v>164</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>185</v>
@@ -6716,7 +6661,7 @@
         <v>165</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>185</v>
@@ -6745,7 +6690,7 @@
         <v>166</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>185</v>
@@ -6774,7 +6719,7 @@
         <v>167</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>185</v>
@@ -6803,7 +6748,7 @@
         <v>168</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>185</v>
@@ -6832,7 +6777,7 @@
         <v>169</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>143</v>
@@ -6861,7 +6806,7 @@
         <v>170</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>185</v>
@@ -6890,7 +6835,7 @@
         <v>171</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>185</v>
@@ -6919,7 +6864,7 @@
         <v>172</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>185</v>
@@ -6948,7 +6893,7 @@
         <v>173</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>185</v>
@@ -6977,7 +6922,7 @@
         <v>174</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>185</v>
@@ -7151,7 +7096,7 @@
         <v>180</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>185</v>
@@ -7180,7 +7125,7 @@
         <v>181</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>185</v>
@@ -7209,7 +7154,7 @@
         <v>182</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>185</v>
@@ -7238,7 +7183,7 @@
         <v>183</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>185</v>
@@ -7267,7 +7212,7 @@
         <v>184</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>143</v>
@@ -7325,7 +7270,7 @@
         <v>188</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>143</v>
@@ -7354,7 +7299,7 @@
         <v>189</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>143</v>
@@ -7383,7 +7328,7 @@
         <v>190</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>143</v>
@@ -7470,7 +7415,7 @@
         <v>195</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>143</v>
@@ -7499,7 +7444,7 @@
         <v>196</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="C50" s="13" t="s">
         <v>143</v>
@@ -7525,10 +7470,10 @@
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="2" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>143</v>
@@ -7554,10 +7499,10 @@
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="2" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>143</v>
@@ -7583,10 +7528,10 @@
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="2" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>143</v>
@@ -7612,10 +7557,10 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>143</v>
@@ -7641,10 +7586,10 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>143</v>
@@ -7670,10 +7615,10 @@
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="2" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>143</v>
@@ -7699,10 +7644,10 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="2" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>143</v>
@@ -7728,10 +7673,10 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>143</v>
@@ -7757,10 +7702,10 @@
     </row>
     <row r="59" spans="1:9">
       <c r="A59" s="2" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>143</v>
@@ -7786,10 +7731,10 @@
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="2" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>143</v>
@@ -7815,10 +7760,10 @@
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="2" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>143</v>
@@ -7844,10 +7789,10 @@
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="2" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>143</v>
@@ -7873,10 +7818,10 @@
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="2" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>143</v>
@@ -7902,10 +7847,10 @@
     </row>
     <row r="64" spans="1:9">
       <c r="A64" s="2" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>143</v>
@@ -7931,10 +7876,10 @@
     </row>
     <row r="65" spans="1:9">
       <c r="A65" s="2" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>143</v>
@@ -7960,10 +7905,10 @@
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="2" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>143</v>
@@ -7989,10 +7934,10 @@
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="2" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>143</v>
@@ -8018,10 +7963,10 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="2" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>143</v>
@@ -8047,10 +7992,10 @@
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="2" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>143</v>
@@ -8076,10 +8021,10 @@
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="2" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>185</v>
@@ -8105,10 +8050,10 @@
     </row>
     <row r="71" spans="1:9">
       <c r="A71" s="2" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>185</v>
@@ -8134,10 +8079,10 @@
     </row>
     <row r="72" spans="1:9">
       <c r="A72" s="2" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>185</v>
@@ -8163,10 +8108,10 @@
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="2" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>185</v>
@@ -8192,10 +8137,10 @@
     </row>
     <row r="74" spans="1:9">
       <c r="A74" s="2" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>185</v>
@@ -8221,10 +8166,10 @@
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="2" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>185</v>
@@ -8250,10 +8195,10 @@
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="2" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>143</v>
@@ -8279,10 +8224,10 @@
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="2" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>143</v>
@@ -8345,7 +8290,7 @@
         <v>200</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>292</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -8368,7 +8313,7 @@
         <v>264</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -8391,7 +8336,7 @@
         <v>223</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -8414,7 +8359,7 @@
         <v>223</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -8437,7 +8382,7 @@
         <v>223</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>283</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8460,7 +8405,7 @@
         <v>223</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -8483,7 +8428,7 @@
         <v>223</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -8506,7 +8451,7 @@
         <v>223</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -8529,7 +8474,7 @@
         <v>223</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>284</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -8552,7 +8497,7 @@
         <v>223</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -8575,7 +8520,7 @@
         <v>223</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -8598,7 +8543,7 @@
         <v>223</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -8621,7 +8566,7 @@
         <v>223</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>286</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -8644,7 +8589,7 @@
         <v>223</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -8667,7 +8612,7 @@
         <v>223</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -8690,7 +8635,7 @@
         <v>223</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -8713,7 +8658,7 @@
         <v>223</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -8736,7 +8681,7 @@
         <v>223</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -8759,15 +8704,15 @@
         <v>223</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>287</v>
+        <v>274</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="2" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>293</v>
+        <v>280</v>
       </c>
       <c r="C20" s="2">
         <v>4</v>
@@ -8782,15 +8727,15 @@
         <v>223</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="2" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="C21" s="2">
         <v>4</v>
@@ -8805,15 +8750,15 @@
         <v>223</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="C22" s="2">
         <v>2</v>
@@ -8828,7 +8773,7 @@
         <v>223</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>285</v>
+        <v>272</v>
       </c>
     </row>
   </sheetData>
@@ -8837,131 +8782,6 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1DEDC361-D738-4510-89A2-AB67CB12EBDF}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="36.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F05608C-89F7-443B-8F02-A238CB7CF577}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9048,7 +8868,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C9E1B61-911D-4E67-9431-CC6DC22C7D98}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -9131,4 +8951,139 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA4966BB-B585-4EFD-A171-2B6D26A10B97}">
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="36.5703125" customWidth="1"/>
+    <col min="2" max="2" width="23.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+    <col min="8" max="8" width="37.42578125" customWidth="1"/>
+    <col min="9" max="9" width="36.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="10">
+        <v>45726.604166666664</v>
+      </c>
+      <c r="C2" s="2">
+        <v>30</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="10">
+        <v>45757.618055555555</v>
+      </c>
+      <c r="C3" s="2">
+        <v>40</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B4" s="10">
+        <v>45758.618055555555</v>
+      </c>
+      <c r="C4" s="2">
+        <v>0</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>